--- a/database/event/4926/event_4926_evp_summary.xlsx
+++ b/database/event/4926/event_4926_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.196</v>
+        <v>6.2652</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3186</v>
+        <v>2.3445</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0817</v>
+        <v>2.0521</v>
       </c>
       <c r="E2" t="n">
-        <v>6.196</v>
+        <v>6.2652</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2503</v>
+        <v>2.844</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9457</v>
+        <v>3.4212</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2503</v>
+        <v>2.844</v>
       </c>
       <c r="I2" t="n">
-        <v>1.824</v>
+        <v>2.3051</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9457</v>
+        <v>3.4212</v>
       </c>
       <c r="K2" t="n">
         <v>86</v>
@@ -529,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7697</v>
+        <v>5.7263</v>
       </c>
       <c r="N2" t="n">
         <v>246</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9416</v>
+        <v>6.196</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2234</v>
+        <v>2.3186</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9789</v>
+        <v>2.0246</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9416</v>
+        <v>6.196</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5204</v>
+        <v>2.2503</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4212</v>
+        <v>3.9457</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5204</v>
+        <v>2.2503</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0429</v>
+        <v>1.824</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4212</v>
+        <v>3.9457</v>
       </c>
       <c r="K3" t="n">
         <v>86</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4641</v>
+        <v>5.7697</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8588</v>
+        <v>6.1871</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1924</v>
+        <v>2.3153</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9455</v>
+        <v>2.021</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8588</v>
+        <v>6.1871</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7775</v>
+        <v>3.1058</v>
       </c>
       <c r="G4" t="n">
         <v>3.0813</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7775</v>
+        <v>3.1058</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2512</v>
+        <v>2.5173</v>
       </c>
       <c r="J4" t="n">
         <v>3.0813</v>
@@ -621,7 +621,7 @@
         <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3325</v>
+        <v>5.5986</v>
       </c>
       <c r="N4" t="n">
         <v>225</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5306</v>
+        <v>4.7177</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6954</v>
+        <v>1.7654</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4089</v>
+        <v>1.4356</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5306</v>
+        <v>4.7177</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5323</v>
+        <v>3.7194</v>
       </c>
       <c r="G5" t="n">
         <v>0.9983</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5323</v>
+        <v>3.7194</v>
       </c>
       <c r="I5" t="n">
-        <v>2.863</v>
+        <v>3.0147</v>
       </c>
       <c r="J5" t="n">
         <v>0.9983</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8613</v>
+        <v>4.013</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3733</v>
+        <v>3.5346</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2623</v>
+        <v>1.3227</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9414</v>
+        <v>0.9643</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3733</v>
+        <v>3.5346</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0931</v>
+        <v>3.1424</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2802</v>
+        <v>0.3922</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0931</v>
+        <v>3.1424</v>
       </c>
       <c r="I6" t="n">
-        <v>0.886</v>
+        <v>2.547</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2802</v>
+        <v>0.3922</v>
       </c>
       <c r="K6" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L6" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1662</v>
+        <v>2.9392</v>
       </c>
       <c r="N6" t="n">
-        <v>246</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2176</v>
+        <v>3.3733</v>
       </c>
       <c r="C7" t="n">
-        <v>1.204</v>
+        <v>1.2623</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2176</v>
+        <v>3.3733</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8254</v>
+        <v>1.0931</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3922</v>
+        <v>2.2802</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8254</v>
+        <v>1.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2901</v>
+        <v>0.886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3922</v>
+        <v>2.2802</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="L7" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6823</v>
+        <v>3.1662</v>
       </c>
       <c r="N7" t="n">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8989</v>
+        <v>3.1692</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0848</v>
+        <v>1.1859</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7497</v>
+        <v>0.8187</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8989</v>
+        <v>3.1692</v>
       </c>
       <c r="F8" t="n">
-        <v>3.505</v>
+        <v>3.7753</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6061</v>
       </c>
       <c r="H8" t="n">
-        <v>3.505</v>
+        <v>3.7753</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8409</v>
+        <v>3.06</v>
       </c>
       <c r="J8" t="n">
         <v>-0.6061</v>
@@ -805,7 +805,7 @@
         <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2348</v>
+        <v>2.4539</v>
       </c>
       <c r="N8" t="n">
         <v>225</v>
@@ -824,7 +824,7 @@
         <v>0.9805</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6371</v>
+        <v>0.5999</v>
       </c>
       <c r="E9" t="n">
         <v>2.6201</v>
@@ -870,7 +870,7 @@
         <v>0.7234</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3596</v>
+        <v>0.3263</v>
       </c>
       <c r="E10" t="n">
         <v>1.9332</v>
@@ -916,7 +916,7 @@
         <v>0.6835</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3165</v>
+        <v>0.2837</v>
       </c>
       <c r="E11" t="n">
         <v>1.8264</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6565</v>
+        <v>1.6615</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6199</v>
+        <v>0.6217</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2478</v>
+        <v>0.218</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6565</v>
+        <v>1.6615</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5006</v>
+        <v>1.5056</v>
       </c>
       <c r="G12" t="n">
         <v>0.1559</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5006</v>
+        <v>1.5056</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2162</v>
+        <v>1.2203</v>
       </c>
       <c r="J12" t="n">
         <v>0.1559</v>
@@ -989,7 +989,7 @@
         <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3721</v>
+        <v>1.3762</v>
       </c>
       <c r="N12" t="n">
         <v>236</v>
@@ -1008,7 +1008,7 @@
         <v>0.6195000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2475</v>
+        <v>0.2157</v>
       </c>
       <c r="E13" t="n">
         <v>1.6556</v>
@@ -1054,7 +1054,7 @@
         <v>0.4911</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1089</v>
+        <v>0.079</v>
       </c>
       <c r="E14" t="n">
         <v>1.3125</v>
@@ -1100,7 +1100,7 @@
         <v>0.4826</v>
       </c>
       <c r="D15" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0699</v>
       </c>
       <c r="E15" t="n">
         <v>1.2897</v>
@@ -1146,7 +1146,7 @@
         <v>0.4003</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0107</v>
+        <v>-0.0178</v>
       </c>
       <c r="E16" t="n">
         <v>1.0696</v>
@@ -1192,7 +1192,7 @@
         <v>0.3595</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0333</v>
+        <v>-0.0612</v>
       </c>
       <c r="E17" t="n">
         <v>0.9607</v>
@@ -1228,415 +1228,415 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8267</v>
+        <v>0.9137</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3094</v>
+        <v>0.3419</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0799</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8267</v>
+        <v>0.9137</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8851</v>
+        <v>0.8416</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0584</v>
+        <v>0.0721</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8851</v>
+        <v>0.8416</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7174</v>
+        <v>0.6822</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0584</v>
+        <v>0.0721</v>
       </c>
       <c r="K18" t="n">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="L18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>0.659</v>
+        <v>0.7543</v>
       </c>
       <c r="N18" t="n">
-        <v>236</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.719</v>
+        <v>0.8267</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2691</v>
+        <v>0.3094</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1309</v>
+        <v>-0.1146</v>
       </c>
       <c r="E19" t="n">
-        <v>0.719</v>
+        <v>0.8267</v>
       </c>
       <c r="F19" t="n">
-        <v>0.719</v>
+        <v>0.8851</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.0584</v>
       </c>
       <c r="H19" t="n">
-        <v>0.719</v>
+        <v>0.8851</v>
       </c>
       <c r="I19" t="n">
-        <v>0.719</v>
+        <v>0.7174</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.0584</v>
       </c>
       <c r="K19" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M19" t="n">
-        <v>0.719</v>
+        <v>0.659</v>
       </c>
       <c r="N19" t="n">
-        <v>155</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.609</v>
+        <v>0.719</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2279</v>
+        <v>0.2691</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1753</v>
+        <v>-0.1575</v>
       </c>
       <c r="E20" t="n">
-        <v>0.609</v>
+        <v>0.719</v>
       </c>
       <c r="F20" t="n">
-        <v>0.609</v>
+        <v>0.719</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.609</v>
+        <v>0.719</v>
       </c>
       <c r="I20" t="n">
-        <v>0.609</v>
+        <v>0.719</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.609</v>
+        <v>0.719</v>
       </c>
       <c r="N20" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5617</v>
+        <v>0.609</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2102</v>
+        <v>0.2279</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1944</v>
+        <v>-0.2013</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5617</v>
+        <v>0.609</v>
       </c>
       <c r="F21" t="n">
-        <v>1.057</v>
+        <v>0.609</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4953</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.057</v>
+        <v>0.609</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8567</v>
+        <v>0.609</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4953</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="L21" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3614</v>
+        <v>0.609</v>
       </c>
       <c r="N21" t="n">
-        <v>246</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4978</v>
+        <v>0.5617</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1863</v>
+        <v>0.2102</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2203</v>
+        <v>-0.2201</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4978</v>
+        <v>0.5617</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4978</v>
+        <v>1.057</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.4953</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4978</v>
+        <v>1.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4978</v>
+        <v>0.8567</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.4953</v>
       </c>
       <c r="K22" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4978</v>
+        <v>0.3614</v>
       </c>
       <c r="N22" t="n">
-        <v>76</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4468</v>
+        <v>0.4978</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1672</v>
+        <v>0.1863</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2409</v>
+        <v>-0.2456</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4468</v>
+        <v>0.4978</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4468</v>
+        <v>0.4978</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4468</v>
+        <v>0.4978</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4468</v>
+        <v>0.4978</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4468</v>
+        <v>0.4978</v>
       </c>
       <c r="N23" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4057</v>
+        <v>0.4468</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1518</v>
+        <v>0.1672</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2575</v>
+        <v>-0.2659</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4057</v>
+        <v>0.4468</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.4468</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2722</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.4468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5495</v>
+        <v>0.4468</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2722</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="L24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2773</v>
+        <v>0.4468</v>
       </c>
       <c r="N24" t="n">
-        <v>201</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3957</v>
+        <v>0.4057</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1481</v>
+        <v>0.1518</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2615</v>
+        <v>-0.2823</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3957</v>
+        <v>0.4057</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3957</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.2722</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3957</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3957</v>
+        <v>0.5495</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.2722</v>
       </c>
       <c r="K25" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3957</v>
+        <v>0.2773</v>
       </c>
       <c r="N25" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3486</v>
+        <v>0.3957</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1304</v>
+        <v>0.1481</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2805</v>
+        <v>-0.2863</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3486</v>
+        <v>0.3957</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2765</v>
+        <v>0.3957</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0721</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2765</v>
+        <v>0.3957</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2241</v>
+        <v>0.3957</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0721</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="L26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2962</v>
+        <v>0.3957</v>
       </c>
       <c r="N26" t="n">
-        <v>201</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27">
@@ -1652,7 +1652,7 @@
         <v>0.0019</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4193</v>
+        <v>-0.4419</v>
       </c>
       <c r="E27" t="n">
         <v>0.0051</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0013</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4228</v>
+        <v>-0.4453</v>
       </c>
       <c r="E28" t="n">
         <v>-0.0035</v>
@@ -1744,7 +1744,7 @@
         <v>-0.035</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4592</v>
+        <v>-0.4812</v>
       </c>
       <c r="E29" t="n">
         <v>-0.0936</v>
@@ -1790,7 +1790,7 @@
         <v>-0.09520000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5241</v>
+        <v>-0.5452</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2543</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1227</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5538</v>
+        <v>-0.5745</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3278</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1341</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5661</v>
+        <v>-0.5867</v>
       </c>
       <c r="E32" t="n">
         <v>-0.3583</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1543</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5879</v>
+        <v>-0.6082</v>
       </c>
       <c r="E33" t="n">
         <v>-0.4123</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1576</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5915</v>
+        <v>-0.6117</v>
       </c>
       <c r="E34" t="n">
         <v>-0.4211</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2105</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6486</v>
+        <v>-0.668</v>
       </c>
       <c r="E35" t="n">
         <v>-0.5624</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2303</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.67</v>
+        <v>-0.6891</v>
       </c>
       <c r="E36" t="n">
         <v>-0.6153999999999999</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2796</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.7416</v>
       </c>
       <c r="E37" t="n">
         <v>-0.7473</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1991</v>
+        <v>-1.1314</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4487</v>
+        <v>-0.4234</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9058</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1991</v>
+        <v>-1.1314</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1991</v>
+        <v>-0.1314</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1991</v>
+        <v>-0.1314</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1614</v>
+        <v>-0.1065</v>
       </c>
       <c r="J38" t="n">
         <v>-1</v>
@@ -2185,7 +2185,7 @@
         <v>75</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1614</v>
+        <v>-1.1065</v>
       </c>
       <c r="N38" t="n">
         <v>236</v>
@@ -2204,7 +2204,7 @@
         <v>-0.6216</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0924</v>
+        <v>-1.1057</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6611</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8008</v>
+        <v>-1.7331</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.6485</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1488</v>
+        <v>-1.1344</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8008</v>
+        <v>-1.7331</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9856</v>
+        <v>-0.9179</v>
       </c>
       <c r="G40" t="n">
         <v>-0.8152</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9856</v>
+        <v>-0.9179</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.744</v>
       </c>
       <c r="J40" t="n">
         <v>-0.8152</v>
@@ -2277,7 +2277,7 @@
         <v>75</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6141</v>
+        <v>-1.5592</v>
       </c>
       <c r="N40" t="n">
         <v>236</v>
@@ -2296,7 +2296,7 @@
         <v>-0.7937</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2782</v>
+        <v>-1.289</v>
       </c>
       <c r="E41" t="n">
         <v>-2.1211</v>

--- a/database/event/4926/event_4926_evp_summary.xlsx
+++ b/database/event/4926/event_4926_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2652</v>
+        <v>6.0647</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3445</v>
+        <v>2.2695</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0521</v>
+        <v>2.0999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2652</v>
+        <v>6.0647</v>
       </c>
       <c r="F2" t="n">
-        <v>2.844</v>
+        <v>2.7258</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4212</v>
+        <v>3.3389</v>
       </c>
       <c r="H2" t="n">
-        <v>2.844</v>
+        <v>4.1179</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3051</v>
+        <v>2.1411</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4212</v>
+        <v>3.3389</v>
       </c>
       <c r="K2" t="n">
         <v>86</v>
@@ -529,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7263</v>
+        <v>5.48</v>
       </c>
       <c r="N2" t="n">
         <v>246</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.196</v>
+        <v>5.8456</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3186</v>
+        <v>2.1875</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0246</v>
+        <v>2.001</v>
       </c>
       <c r="E3" t="n">
-        <v>6.196</v>
+        <v>5.8456</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2503</v>
+        <v>2.8128</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9457</v>
+        <v>3.0328</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2503</v>
+        <v>4.4242</v>
       </c>
       <c r="I3" t="n">
-        <v>1.824</v>
+        <v>2.3004</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9457</v>
+        <v>3.0328</v>
       </c>
       <c r="K3" t="n">
         <v>86</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>5.7697</v>
+        <v>5.3332</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1871</v>
+        <v>5.4559</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3153</v>
+        <v>2.0416</v>
       </c>
       <c r="D4" t="n">
-        <v>2.021</v>
+        <v>1.8251</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1871</v>
+        <v>5.4559</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1058</v>
+        <v>2.9643</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0813</v>
+        <v>2.4916</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1058</v>
+        <v>4.9579</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5173</v>
+        <v>2.5779</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0813</v>
+        <v>2.4916</v>
       </c>
       <c r="K4" t="n">
         <v>70</v>
@@ -621,7 +621,7 @@
         <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5986</v>
+        <v>5.0695</v>
       </c>
       <c r="N4" t="n">
         <v>225</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7177</v>
+        <v>4.0552</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7654</v>
+        <v>1.5175</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4356</v>
+        <v>1.1927</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7177</v>
+        <v>4.0552</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7194</v>
+        <v>3.2908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9983</v>
+        <v>0.7644</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7194</v>
+        <v>6.1084</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0147</v>
+        <v>3.1761</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9983</v>
+        <v>0.7644</v>
       </c>
       <c r="K5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>4.013</v>
+        <v>3.9405</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5346</v>
+        <v>3.9537</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3227</v>
+        <v>1.4795</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9643</v>
+        <v>1.1469</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5346</v>
+        <v>3.9537</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1424</v>
+        <v>1.9725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3922</v>
+        <v>1.9812</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1424</v>
+        <v>1.9725</v>
       </c>
       <c r="I6" t="n">
-        <v>2.547</v>
+        <v>1.0256</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3922</v>
+        <v>1.9812</v>
       </c>
       <c r="K6" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="L6" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9392</v>
+        <v>3.0068</v>
       </c>
       <c r="N6" t="n">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3733</v>
+        <v>3.4911</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2623</v>
+        <v>1.3064</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3733</v>
+        <v>3.4911</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0931</v>
+        <v>2.991</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2802</v>
+        <v>0.5001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0931</v>
+        <v>5.052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.886</v>
+        <v>2.6268</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2802</v>
+        <v>0.5001</v>
       </c>
       <c r="K7" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1662</v>
+        <v>3.1269</v>
       </c>
       <c r="N7" t="n">
-        <v>246</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1692</v>
+        <v>3.0302</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1859</v>
+        <v>1.1339</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8187</v>
+        <v>0.73</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1692</v>
+        <v>3.0302</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7753</v>
+        <v>3.3231</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6061</v>
+        <v>-0.2929</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7753</v>
+        <v>6.2223</v>
       </c>
       <c r="I8" t="n">
-        <v>3.06</v>
+        <v>3.2353</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6061</v>
+        <v>-0.2929</v>
       </c>
       <c r="K8" t="n">
         <v>70</v>
@@ -805,7 +805,7 @@
         <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4539</v>
+        <v>2.9424</v>
       </c>
       <c r="N8" t="n">
         <v>225</v>
@@ -814,277 +814,277 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6201</v>
+        <v>2.7514</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9805</v>
+        <v>1.0296</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5999</v>
+        <v>0.6041</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6201</v>
+        <v>2.7514</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0365</v>
+        <v>2.6153</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6566</v>
+        <v>0.1361</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0365</v>
+        <v>3.7284</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0296</v>
+        <v>1.9386</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6566</v>
+        <v>0.1361</v>
       </c>
       <c r="K9" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="L9" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>2.627</v>
+        <v>2.0747</v>
       </c>
       <c r="N9" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9332</v>
+        <v>2.6237</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7234</v>
+        <v>0.9818</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3263</v>
+        <v>0.5465</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9332</v>
+        <v>2.6237</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8713</v>
+        <v>0.33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0619</v>
+        <v>2.2937</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8713</v>
+        <v>0.33</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5167</v>
+        <v>0.1716</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0619</v>
+        <v>2.2937</v>
       </c>
       <c r="K10" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5786</v>
+        <v>2.4653</v>
       </c>
       <c r="N10" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8264</v>
+        <v>2.5655</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6835</v>
+        <v>0.96</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2837</v>
+        <v>0.5202</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8264</v>
+        <v>2.5655</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8264</v>
+        <v>2.0879</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.4776</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8264</v>
+        <v>2.0879</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8264</v>
+        <v>1.0856</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.4776</v>
       </c>
       <c r="K11" t="n">
         <v>131</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8264</v>
+        <v>1.5632</v>
       </c>
       <c r="N11" t="n">
-        <v>131</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6615</v>
+        <v>2.2744</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6217</v>
+        <v>0.8511</v>
       </c>
       <c r="D12" t="n">
-        <v>0.218</v>
+        <v>0.3888</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6615</v>
+        <v>2.2744</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5056</v>
+        <v>2.2744</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1559</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5056</v>
+        <v>2.2744</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2203</v>
+        <v>2.2744</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1559</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="L12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3762</v>
+        <v>2.2744</v>
       </c>
       <c r="N12" t="n">
-        <v>236</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6556</v>
+        <v>2.2669</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2157</v>
+        <v>0.3854</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6556</v>
+        <v>2.2669</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6556</v>
+        <v>2.1681</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.0988</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6556</v>
+        <v>2.1681</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6556</v>
+        <v>1.1273</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.0988</v>
       </c>
       <c r="K13" t="n">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6556</v>
+        <v>1.2261</v>
       </c>
       <c r="N13" t="n">
-        <v>131</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3125</v>
+        <v>2.1642</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4911</v>
+        <v>0.8099</v>
       </c>
       <c r="D14" t="n">
-        <v>0.079</v>
+        <v>0.339</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3125</v>
+        <v>2.1642</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8781</v>
+        <v>2.1642</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4344</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8781</v>
+        <v>2.1642</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7117</v>
+        <v>2.1642</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4344</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>131</v>
       </c>
       <c r="L14" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1461</v>
+        <v>2.1642</v>
       </c>
       <c r="N14" t="n">
-        <v>201</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2897</v>
+        <v>2.1039</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4826</v>
+        <v>0.7873</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0699</v>
+        <v>0.3118</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2897</v>
+        <v>2.1039</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7232</v>
+        <v>1.6567</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5665</v>
+        <v>0.4472</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7232</v>
+        <v>1.6567</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5665</v>
+        <v>0.4472</v>
       </c>
       <c r="K15" t="n">
         <v>131</v>
@@ -1127,7 +1127,7 @@
         <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1527</v>
+        <v>1.3086</v>
       </c>
       <c r="N15" t="n">
         <v>201</v>
@@ -1136,81 +1136,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0696</v>
+        <v>1.9349</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4003</v>
+        <v>0.7241</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0178</v>
+        <v>0.2355</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0696</v>
+        <v>1.9349</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0696</v>
+        <v>2.4482</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.5133</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0696</v>
+        <v>3.1397</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0696</v>
+        <v>1.6325</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.5133</v>
       </c>
       <c r="K16" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0696</v>
+        <v>1.1192</v>
       </c>
       <c r="N16" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9607</v>
+        <v>1.9306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3595</v>
+        <v>0.7224</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0612</v>
+        <v>0.2336</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9607</v>
+        <v>1.9306</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7614</v>
+        <v>2.0604</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8007</v>
+        <v>-0.1298</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7614</v>
+        <v>2.0604</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4277</v>
+        <v>1.0713</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8007</v>
+        <v>-0.1298</v>
       </c>
       <c r="K17" t="n">
         <v>131</v>
@@ -1219,7 +1219,7 @@
         <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>0.627</v>
+        <v>0.9414999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>201</v>
@@ -1228,369 +1228,369 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9137</v>
+        <v>1.8261</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3419</v>
+        <v>0.6833</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0799</v>
+        <v>0.1864</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9137</v>
+        <v>1.8261</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8416</v>
+        <v>1.855</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0721</v>
+        <v>-0.0289</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8416</v>
+        <v>1.855</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6822</v>
+        <v>0.9645</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0721</v>
+        <v>-0.0289</v>
       </c>
       <c r="K18" t="n">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="L18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7543</v>
+        <v>0.9356</v>
       </c>
       <c r="N18" t="n">
-        <v>201</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8267</v>
+        <v>1.5829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3094</v>
+        <v>0.5923</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1146</v>
+        <v>0.0766</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8267</v>
+        <v>1.5829</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8851</v>
+        <v>1.7938</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0584</v>
+        <v>-0.2109</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8851</v>
+        <v>1.7938</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7174</v>
+        <v>0.9327</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0584</v>
+        <v>-0.2109</v>
       </c>
       <c r="K19" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="L19" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="M19" t="n">
-        <v>0.659</v>
+        <v>0.7218</v>
       </c>
       <c r="N19" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.719</v>
+        <v>1.5783</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2691</v>
+        <v>0.5906</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1575</v>
+        <v>0.0745</v>
       </c>
       <c r="E20" t="n">
-        <v>0.719</v>
+        <v>1.5783</v>
       </c>
       <c r="F20" t="n">
-        <v>0.719</v>
+        <v>1.4582</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1201</v>
       </c>
       <c r="H20" t="n">
-        <v>0.719</v>
+        <v>1.4582</v>
       </c>
       <c r="I20" t="n">
-        <v>0.719</v>
+        <v>0.7582</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1201</v>
       </c>
       <c r="K20" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M20" t="n">
-        <v>0.719</v>
+        <v>0.8783</v>
       </c>
       <c r="N20" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.609</v>
+        <v>1.4707</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2279</v>
+        <v>0.5503</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2013</v>
+        <v>0.0259</v>
       </c>
       <c r="E21" t="n">
-        <v>0.609</v>
+        <v>1.4707</v>
       </c>
       <c r="F21" t="n">
-        <v>0.609</v>
+        <v>1.4707</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.609</v>
+        <v>1.4707</v>
       </c>
       <c r="I21" t="n">
-        <v>0.609</v>
+        <v>1.4707</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.609</v>
+        <v>1.4707</v>
       </c>
       <c r="N21" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5617</v>
+        <v>1.1759</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2102</v>
+        <v>0.44</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2201</v>
+        <v>-0.1072</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5617</v>
+        <v>1.1759</v>
       </c>
       <c r="F22" t="n">
-        <v>1.057</v>
+        <v>1.1759</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4953</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.057</v>
+        <v>1.1759</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8567</v>
+        <v>1.1759</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4953</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="L22" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3614</v>
+        <v>1.1759</v>
       </c>
       <c r="N22" t="n">
-        <v>246</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4978</v>
+        <v>1.0182</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1863</v>
+        <v>0.381</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2456</v>
+        <v>-0.1783</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4978</v>
+        <v>1.0182</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4978</v>
+        <v>1.0182</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4978</v>
+        <v>1.0182</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4978</v>
+        <v>1.0182</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4978</v>
+        <v>1.0182</v>
       </c>
       <c r="N23" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4468</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1672</v>
+        <v>0.2816</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2659</v>
+        <v>-0.2983</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4468</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4468</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4468</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4468</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4468</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4057</v>
+        <v>0.6879</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1518</v>
+        <v>0.2574</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2823</v>
+        <v>-0.3275</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4057</v>
+        <v>0.6879</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6879</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2722</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6879</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5495</v>
+        <v>0.6879</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2722</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="L25" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2773</v>
+        <v>0.6879</v>
       </c>
       <c r="N25" t="n">
-        <v>201</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3957</v>
+        <v>0.6482</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1481</v>
+        <v>0.2426</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2863</v>
+        <v>-0.3454</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3957</v>
+        <v>0.6482</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3957</v>
+        <v>0.6482</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3957</v>
+        <v>0.6482</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3957</v>
+        <v>0.6482</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3957</v>
+        <v>0.6482</v>
       </c>
       <c r="N26" t="n">
         <v>155</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0051</v>
+        <v>0.3786</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0019</v>
+        <v>0.1417</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4419</v>
+        <v>-0.4671</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0051</v>
+        <v>0.3786</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0051</v>
+        <v>1.4926</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1.114</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0051</v>
+        <v>1.4926</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0051</v>
+        <v>0.7761</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1.114</v>
       </c>
       <c r="K27" t="n">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0051</v>
+        <v>-0.3379000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>131</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>leo_drk</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0035</v>
+        <v>0.3642</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0013</v>
+        <v>0.1363</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4453</v>
+        <v>-0.4736</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0035</v>
+        <v>0.3642</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0035</v>
+        <v>0.3642</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0035</v>
+        <v>0.3642</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0035</v>
+        <v>0.3642</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0035</v>
+        <v>0.3642</v>
       </c>
       <c r="N28" t="n">
-        <v>86</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0936</v>
+        <v>0.2344</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.035</v>
+        <v>0.0877</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4812</v>
+        <v>-0.5322</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0936</v>
+        <v>0.2344</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0936</v>
+        <v>0.2344</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0936</v>
+        <v>0.2344</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0936</v>
+        <v>0.2344</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0936</v>
+        <v>0.2344</v>
       </c>
       <c r="N29" t="n">
         <v>86</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>leo_drk</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2543</v>
+        <v>0.2222</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5452</v>
+        <v>-0.5377</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2543</v>
+        <v>0.2222</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2543</v>
+        <v>0.2222</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2543</v>
+        <v>0.2222</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2543</v>
+        <v>0.2222</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2543</v>
+        <v>0.2222</v>
       </c>
       <c r="N30" t="n">
         <v>86</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jnt</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3278</v>
+        <v>-0.0378</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1227</v>
+        <v>-0.0141</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5745</v>
+        <v>-0.6551</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3278</v>
+        <v>-0.0378</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3278</v>
+        <v>-0.0378</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3278</v>
+        <v>-0.0378</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3278</v>
+        <v>-0.0378</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3278</v>
+        <v>-0.0378</v>
       </c>
       <c r="N31" t="n">
         <v>86</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3583</v>
+        <v>-0.0674</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1341</v>
+        <v>-0.0252</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5867</v>
+        <v>-0.6684</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3583</v>
+        <v>-0.0674</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3583</v>
+        <v>-0.0674</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3583</v>
+        <v>-0.0674</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3583</v>
+        <v>-0.0674</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3583</v>
+        <v>-0.0674</v>
       </c>
       <c r="N32" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4123</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1543</v>
+        <v>-0.0273</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6082</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4123</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4123</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4123</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4123</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4123</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>jnt</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4211</v>
+        <v>-0.1784</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1576</v>
+        <v>-0.0668</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6117</v>
+        <v>-0.7186</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4211</v>
+        <v>-0.1784</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4211</v>
+        <v>-0.1784</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4211</v>
+        <v>-0.1784</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4211</v>
+        <v>-0.1784</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4211</v>
+        <v>-0.1784</v>
       </c>
       <c r="N34" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5624</v>
+        <v>-0.2143</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2105</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.668</v>
+        <v>-0.7348</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5624</v>
+        <v>-0.2143</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5624</v>
+        <v>-0.2143</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5624</v>
+        <v>-0.2143</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5624</v>
+        <v>-0.2143</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5624</v>
+        <v>-0.2143</v>
       </c>
       <c r="N35" t="n">
-        <v>131</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3492</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2303</v>
+        <v>-0.1307</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.6891</v>
+        <v>-0.7957</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3492</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3492</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3492</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3492</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3492</v>
       </c>
       <c r="N36" t="n">
         <v>76</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7473</v>
+        <v>-0.3521</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2796</v>
+        <v>-0.1318</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7416</v>
+        <v>-0.797</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7473</v>
+        <v>-0.3521</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5911</v>
+        <v>-0.3521</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.3384</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5911</v>
+        <v>-0.3521</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4791</v>
+        <v>-0.3521</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.3384</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="L37" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8593</v>
+        <v>-0.3521</v>
       </c>
       <c r="N37" t="n">
-        <v>225</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1314</v>
+        <v>-0.4055</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4234</v>
+        <v>-0.1517</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1314</v>
+        <v>-0.4055</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1314</v>
+        <v>0.5945</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1314</v>
+        <v>0.5945</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1065</v>
+        <v>0.3091</v>
       </c>
       <c r="J38" t="n">
         <v>-1</v>
@@ -2185,7 +2185,7 @@
         <v>75</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1065</v>
+        <v>-0.6909000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>236</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6611</v>
+        <v>-1.1883</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6216</v>
+        <v>-0.4447</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1057</v>
+        <v>-1.1745</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6611</v>
+        <v>-1.1883</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6611</v>
+        <v>-1.1883</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6611</v>
+        <v>-1.1883</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6611</v>
+        <v>-1.1883</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6611</v>
+        <v>-1.1883</v>
       </c>
       <c r="N39" t="n">
         <v>76</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7331</v>
+        <v>-1.3601</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6485</v>
+        <v>-0.509</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1344</v>
+        <v>-1.252</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7331</v>
+        <v>-1.3601</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9179</v>
+        <v>-0.8691</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8152</v>
+        <v>-0.491</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9179</v>
+        <v>-0.8691</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.744</v>
+        <v>-0.4519</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8152</v>
+        <v>-0.491</v>
       </c>
       <c r="K40" t="n">
         <v>161</v>
@@ -2277,7 +2277,7 @@
         <v>75</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5592</v>
+        <v>-0.9429000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>236</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1211</v>
+        <v>-1.9104</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7937</v>
+        <v>-0.7149</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.289</v>
+        <v>-1.5005</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1211</v>
+        <v>-1.9104</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1211</v>
+        <v>-1.9104</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1211</v>
+        <v>-1.9104</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.1211</v>
+        <v>-1.9104</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1211</v>
+        <v>-1.9104</v>
       </c>
       <c r="N41" t="n">
         <v>131</v>
@@ -2429,10 +2429,10 @@
         <v>1.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1861</v>
+        <v>0.1541</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3274</v>
+        <v>5.2394</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1279</v>
+        <v>0.1043</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3486</v>
+        <v>3.5462</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1279</v>
+        <v>0.1043</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3486</v>
+        <v>3.5462</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.99</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0495</v>
+        <v>-0.0218</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.683</v>
+        <v>-0.7412</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2156</v>
+        <v>-0.1248</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.3304</v>
+        <v>-4.2432</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.64</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8958</v>
+        <v>0.8122</v>
       </c>
       <c r="J7" t="n">
-        <v>30.4572</v>
+        <v>27.6148</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2498</v>
+        <v>0.2062</v>
       </c>
       <c r="J8" t="n">
-        <v>8.4932</v>
+        <v>7.0108</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1111</v>
+        <v>0.1074</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7774</v>
+        <v>3.6516</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3262</v>
+        <v>-0.196</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.0908</v>
+        <v>-6.664</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5575</v>
+        <v>-0.3627</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.955</v>
+        <v>-12.3318</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4817</v>
+        <v>1.3092</v>
       </c>
       <c r="J12" t="n">
-        <v>40.0059</v>
+        <v>35.3484</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8197</v>
+        <v>0.7994</v>
       </c>
       <c r="J13" t="n">
-        <v>22.1319</v>
+        <v>21.5838</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.296</v>
+        <v>0.3218</v>
       </c>
       <c r="J14" t="n">
-        <v>7.992</v>
+        <v>8.688599999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5016</v>
+        <v>-0.4371</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.5432</v>
+        <v>-11.8017</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.67</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0009</v>
+        <v>-0.9762</v>
       </c>
       <c r="J16" t="n">
-        <v>-27.0243</v>
+        <v>-26.3574</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2515</v>
+        <v>0.2641</v>
       </c>
       <c r="J17" t="n">
-        <v>6.7905</v>
+        <v>7.1307</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001</v>
+        <v>-0.0152</v>
       </c>
       <c r="J18" t="n">
-        <v>0.027</v>
+        <v>-0.4104</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001</v>
+        <v>-0.0152</v>
       </c>
       <c r="J19" t="n">
-        <v>0.027</v>
+        <v>-0.4104</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0718</v>
+        <v>-0.0584</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9386</v>
+        <v>-1.5768</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5733</v>
+        <v>-0.3761</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.4791</v>
+        <v>-10.1547</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.89</v>
       </c>
       <c r="I22" t="n">
-        <v>1.897</v>
+        <v>1.5967</v>
       </c>
       <c r="J22" t="n">
-        <v>45.528</v>
+        <v>38.3208</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.9079</v>
       </c>
       <c r="J23" t="n">
-        <v>21.2544</v>
+        <v>21.7896</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6223</v>
+        <v>0.6877</v>
       </c>
       <c r="J24" t="n">
-        <v>14.9352</v>
+        <v>16.5048</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0542</v>
+        <v>0.1334</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3008</v>
+        <v>3.2016</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6762</v>
+        <v>-0.6147</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.2288</v>
+        <v>-14.7528</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4914</v>
+        <v>0.5736</v>
       </c>
       <c r="J27" t="n">
-        <v>11.7936</v>
+        <v>13.7664</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1154</v>
+        <v>0.0915</v>
       </c>
       <c r="J28" t="n">
-        <v>2.7696</v>
+        <v>2.196</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0206</v>
+        <v>-0.0091</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4944</v>
+        <v>-0.2184</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.89</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1975</v>
+        <v>-0.1343</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.74</v>
+        <v>-3.2232</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.32</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9545</v>
+        <v>-0.6694</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.908</v>
+        <v>-16.0656</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.02</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1706</v>
+        <v>0.112</v>
       </c>
       <c r="J32" t="n">
-        <v>3.7532</v>
+        <v>2.464</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.92</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.068</v>
+        <v>-0.0796</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.496</v>
+        <v>-1.7512</v>
       </c>
     </row>
     <row r="34">
@@ -3749,10 +3749,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.57</v>
+        <v>-0.3803</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.54</v>
+        <v>-8.3666</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.35</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9069</v>
+        <v>-0.6302</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.9518</v>
+        <v>-13.8644</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.54</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7069</v>
+        <v>0.5141</v>
       </c>
       <c r="J37" t="n">
-        <v>15.5518</v>
+        <v>11.3102</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.45</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6004</v>
+        <v>0.4585</v>
       </c>
       <c r="J38" t="n">
-        <v>13.2088</v>
+        <v>10.087</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.42</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5628</v>
+        <v>0.4398</v>
       </c>
       <c r="J39" t="n">
-        <v>12.3816</v>
+        <v>9.675599999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.402</v>
+        <v>0.3706</v>
       </c>
       <c r="J40" t="n">
-        <v>8.843999999999999</v>
+        <v>8.1532</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0197</v>
+        <v>0.0246</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4334</v>
+        <v>0.5412</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2081</v>
+        <v>0.8689</v>
       </c>
       <c r="J42" t="n">
-        <v>26.5782</v>
+        <v>19.1158</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.51</v>
       </c>
       <c r="I43" t="n">
-        <v>1.188</v>
+        <v>0.8565</v>
       </c>
       <c r="J43" t="n">
-        <v>26.136</v>
+        <v>18.843</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.38</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9113</v>
+        <v>0.6933</v>
       </c>
       <c r="J44" t="n">
-        <v>20.0486</v>
+        <v>15.2526</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.19</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4257</v>
+        <v>0.4402</v>
       </c>
       <c r="J45" t="n">
-        <v>9.365399999999999</v>
+        <v>9.6844</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.96</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3287</v>
+        <v>-0.2438</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.2314</v>
+        <v>-5.3636</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.87</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1475</v>
+        <v>-0.1345</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.245</v>
+        <v>-2.959</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.84</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1976</v>
+        <v>-0.1673</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.3472</v>
+        <v>-3.6806</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.77</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.315</v>
+        <v>-0.2384</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.93</v>
+        <v>-5.2448</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4467</v>
+        <v>-0.3029</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.827400000000001</v>
+        <v>-6.6638</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6591</v>
+        <v>-0.4433</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.5002</v>
+        <v>-9.752599999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.35</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9624</v>
+        <v>0.695</v>
       </c>
       <c r="J52" t="n">
-        <v>25.0224</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.26</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7572</v>
+        <v>0.5687</v>
       </c>
       <c r="J53" t="n">
-        <v>19.6872</v>
+        <v>14.7862</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7572</v>
+        <v>0.5687</v>
       </c>
       <c r="J54" t="n">
-        <v>19.6872</v>
+        <v>14.7862</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3524</v>
+        <v>-0.2866</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.1624</v>
+        <v>-7.4516</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.976</v>
+        <v>-0.9486</v>
       </c>
       <c r="J56" t="n">
-        <v>-25.376</v>
+        <v>-24.6636</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3183</v>
+        <v>0.3407</v>
       </c>
       <c r="J57" t="n">
-        <v>8.2758</v>
+        <v>8.8582</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1637</v>
+        <v>0.156</v>
       </c>
       <c r="J58" t="n">
-        <v>4.2562</v>
+        <v>4.056</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1824</v>
+        <v>-0.116</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.7424</v>
+        <v>-3.016</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.32</v>
+        <v>-0.2006</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.32</v>
+        <v>-5.2156</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.466</v>
+        <v>-0.2995</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.116</v>
+        <v>-7.787</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.42</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0139</v>
+        <v>0.748</v>
       </c>
       <c r="J62" t="n">
-        <v>24.3336</v>
+        <v>17.952</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9263</v>
+        <v>0.6969</v>
       </c>
       <c r="J63" t="n">
-        <v>22.2312</v>
+        <v>16.7256</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.32</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>18.8592</v>
+        <v>14.868</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.19</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4375</v>
+        <v>0.4435</v>
       </c>
       <c r="J65" t="n">
-        <v>10.5</v>
+        <v>10.644</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2547</v>
+        <v>0.3337</v>
       </c>
       <c r="J66" t="n">
-        <v>6.1128</v>
+        <v>8.008800000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.08</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2863</v>
+        <v>0.296</v>
       </c>
       <c r="J67" t="n">
-        <v>6.8712</v>
+        <v>7.104</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0698</v>
+        <v>-0.0805</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.6752</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3747</v>
+        <v>-0.2588</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.992800000000001</v>
+        <v>-6.2112</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6513</v>
+        <v>-0.437</v>
       </c>
       <c r="J70" t="n">
-        <v>-15.6312</v>
+        <v>-10.488</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.52</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7026</v>
+        <v>-0.4742</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.8624</v>
+        <v>-11.3808</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4953</v>
+        <v>0.4004</v>
       </c>
       <c r="J72" t="n">
-        <v>14.3637</v>
+        <v>11.6116</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.18</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3558</v>
+        <v>0.308</v>
       </c>
       <c r="J73" t="n">
-        <v>10.3182</v>
+        <v>8.932</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2121</v>
+        <v>0.1736</v>
       </c>
       <c r="J74" t="n">
-        <v>6.1509</v>
+        <v>5.0344</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.73</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4799</v>
+        <v>-0.3072</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.9171</v>
+        <v>-8.908799999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.7</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5195</v>
+        <v>-0.3358</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.0655</v>
+        <v>-9.738200000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4837</v>
+        <v>0.3809</v>
       </c>
       <c r="J77" t="n">
-        <v>14.0273</v>
+        <v>11.0461</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3591</v>
+        <v>0.3038</v>
       </c>
       <c r="J78" t="n">
-        <v>10.4139</v>
+        <v>8.8102</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2824</v>
+        <v>0.2405</v>
       </c>
       <c r="J79" t="n">
-        <v>8.1896</v>
+        <v>6.9745</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.98</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1081</v>
+        <v>-0.0469</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.1349</v>
+        <v>-1.3601</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2404</v>
+        <v>-0.1352</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.9716</v>
+        <v>-3.9208</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.48</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0936</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>24.0592</v>
+        <v>17.798</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>0.915</v>
+        <v>0.711</v>
       </c>
       <c r="J83" t="n">
-        <v>20.13</v>
+        <v>15.642</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.39</v>
       </c>
       <c r="I84" t="n">
-        <v>0.89</v>
+        <v>0.6988</v>
       </c>
       <c r="J84" t="n">
-        <v>19.58</v>
+        <v>15.3736</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8299</v>
+        <v>0.6747</v>
       </c>
       <c r="J85" t="n">
-        <v>18.2578</v>
+        <v>14.8434</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.25</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5433</v>
+        <v>0.5174</v>
       </c>
       <c r="J86" t="n">
-        <v>11.9526</v>
+        <v>11.3828</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.97</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0339</v>
+        <v>-0.0106</v>
       </c>
       <c r="J87" t="n">
-        <v>0.7458</v>
+        <v>-0.2332</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.89</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1163</v>
+        <v>-0.113</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.5586</v>
+        <v>-2.486</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1334</v>
+        <v>-0.1245</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.9348</v>
+        <v>-2.739</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6476</v>
+        <v>-0.4349</v>
       </c>
       <c r="J90" t="n">
-        <v>-14.2472</v>
+        <v>-9.5678</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.46</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7744</v>
+        <v>-0.5278</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.0368</v>
+        <v>-11.6116</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.95</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9492</v>
+        <v>1.6466</v>
       </c>
       <c r="J92" t="n">
-        <v>48.73</v>
+        <v>41.165</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.27</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6062</v>
+        <v>0.6986</v>
       </c>
       <c r="J93" t="n">
-        <v>15.155</v>
+        <v>17.465</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.26</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6755</v>
       </c>
       <c r="J94" t="n">
-        <v>14.555</v>
+        <v>16.8875</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.24</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5342</v>
+        <v>0.6287</v>
       </c>
       <c r="J95" t="n">
-        <v>13.355</v>
+        <v>15.7175</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1679</v>
+        <v>-0.0828</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.1975</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.29</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5867</v>
+        <v>0.7113</v>
       </c>
       <c r="J97" t="n">
-        <v>14.6675</v>
+        <v>17.7825</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1341</v>
+        <v>-0.1208</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.3525</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.74</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4049</v>
+        <v>-0.2711</v>
       </c>
       <c r="J99" t="n">
-        <v>-10.1225</v>
+        <v>-6.7775</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.62</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5784</v>
+        <v>-0.3845</v>
       </c>
       <c r="J100" t="n">
-        <v>-14.46</v>
+        <v>-9.612500000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.41</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8409</v>
+        <v>-0.5786</v>
       </c>
       <c r="J101" t="n">
-        <v>-21.0225</v>
+        <v>-14.465</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.24</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6985</v>
+        <v>0.6775</v>
       </c>
       <c r="J102" t="n">
-        <v>20.2565</v>
+        <v>19.6475</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.22</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6488</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>18.8152</v>
+        <v>18.2265</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6488</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="J104" t="n">
-        <v>18.8152</v>
+        <v>18.2265</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.016</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>0.464</v>
+        <v>2.0039</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.87</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5299</v>
+        <v>-0.4661</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.3671</v>
+        <v>-13.5169</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5161</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>14.9669</v>
+        <v>17.6146</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0075</v>
+        <v>-0.0261</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.2175</v>
+        <v>-0.7569</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.88</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.222</v>
+        <v>-0.1452</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.438</v>
+        <v>-4.2108</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4152</v>
+        <v>-0.2663</v>
       </c>
       <c r="J110" t="n">
-        <v>-12.0408</v>
+        <v>-7.7227</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6169</v>
+        <v>-0.4087</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.8901</v>
+        <v>-11.8523</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.16</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3549</v>
+        <v>0.3006</v>
       </c>
       <c r="J112" t="n">
-        <v>9.5823</v>
+        <v>8.116199999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.96</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0602</v>
+        <v>-0.0561</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.6254</v>
+        <v>-1.5147</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1458</v>
+        <v>-0.1039</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.9366</v>
+        <v>-2.8053</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.86</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2654</v>
+        <v>-0.1678</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.1658</v>
+        <v>-4.5306</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5298</v>
+        <v>-0.3452</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.3046</v>
+        <v>-9.320399999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.4762</v>
       </c>
       <c r="J117" t="n">
-        <v>14.6016</v>
+        <v>12.8574</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.3</v>
       </c>
       <c r="I118" t="n">
-        <v>0.449</v>
+        <v>0.3967</v>
       </c>
       <c r="J118" t="n">
-        <v>12.123</v>
+        <v>10.7109</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3281</v>
+        <v>0.3039</v>
       </c>
       <c r="J119" t="n">
-        <v>8.858700000000001</v>
+        <v>8.205299999999999</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2425</v>
+        <v>0.2435</v>
       </c>
       <c r="J120" t="n">
-        <v>6.5475</v>
+        <v>6.5745</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.03</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0046</v>
+        <v>0.0402</v>
       </c>
       <c r="J121" t="n">
-        <v>0.1242</v>
+        <v>1.0854</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.74</v>
       </c>
       <c r="I122" t="n">
-        <v>1.6888</v>
+        <v>1.4506</v>
       </c>
       <c r="J122" t="n">
-        <v>50.664</v>
+        <v>43.518</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2793</v>
+        <v>0.3363</v>
       </c>
       <c r="J123" t="n">
-        <v>8.379</v>
+        <v>10.089</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2498</v>
+        <v>0.3085</v>
       </c>
       <c r="J124" t="n">
-        <v>7.494</v>
+        <v>9.255000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0611</v>
+        <v>0.1257</v>
       </c>
       <c r="J125" t="n">
-        <v>1.833</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5226</v>
+        <v>-0.454</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.678</v>
+        <v>-13.62</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1959</v>
+        <v>0.2068</v>
       </c>
       <c r="J127" t="n">
-        <v>5.877</v>
+        <v>6.204</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.04</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1182</v>
+        <v>0.1176</v>
       </c>
       <c r="J128" t="n">
-        <v>3.546</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="J129" t="n">
-        <v>2.172</v>
+        <v>2.022</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.93</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1714</v>
+        <v>-0.0992</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.142</v>
+        <v>-2.976</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.89</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2423</v>
+        <v>-0.1444</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.269</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.83</v>
       </c>
       <c r="I132" t="n">
-        <v>1.8508</v>
+        <v>1.5641</v>
       </c>
       <c r="J132" t="n">
-        <v>51.8224</v>
+        <v>43.7948</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5341</v>
+        <v>0.5414</v>
       </c>
       <c r="J133" t="n">
-        <v>14.9548</v>
+        <v>15.1592</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1101</v>
+        <v>-0.04</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.0828</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4087</v>
+        <v>-0.3358</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.4436</v>
+        <v>-9.4024</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4932</v>
+        <v>-0.4236</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.8096</v>
+        <v>-11.8608</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4537</v>
+        <v>0.5216</v>
       </c>
       <c r="J137" t="n">
-        <v>12.7036</v>
+        <v>14.6048</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2162</v>
+        <v>0.2089</v>
       </c>
       <c r="J138" t="n">
-        <v>6.0536</v>
+        <v>5.8492</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.24</v>
+        <v>-0.1714</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.72</v>
+        <v>-4.7992</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.58</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6445</v>
+        <v>-0.4299</v>
       </c>
       <c r="J140" t="n">
-        <v>-18.046</v>
+        <v>-12.0372</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6944</v>
+        <v>-0.4668</v>
       </c>
       <c r="J141" t="n">
-        <v>-19.4432</v>
+        <v>-13.0704</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4521</v>
+        <v>0.5372</v>
       </c>
       <c r="J142" t="n">
-        <v>13.1109</v>
+        <v>15.5788</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.17</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3084</v>
+        <v>0.361</v>
       </c>
       <c r="J143" t="n">
-        <v>8.9436</v>
+        <v>10.469</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2606</v>
+        <v>0.3057</v>
       </c>
       <c r="J144" t="n">
-        <v>7.5574</v>
+        <v>8.8653</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1009</v>
+        <v>-0.0443</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.9261</v>
+        <v>-1.2847</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2987</v>
+        <v>-0.1764</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.6623</v>
+        <v>-5.1156</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0977</v>
+        <v>1.0537</v>
       </c>
       <c r="J147" t="n">
-        <v>31.8333</v>
+        <v>30.5573</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.396</v>
+        <v>0.38</v>
       </c>
       <c r="J148" t="n">
-        <v>11.484</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1104</v>
+        <v>0.1476</v>
       </c>
       <c r="J149" t="n">
-        <v>3.2016</v>
+        <v>4.2804</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0711</v>
+        <v>-0.0188</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.0619</v>
+        <v>-0.5452</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5719</v>
+        <v>-0.5128</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.5851</v>
+        <v>-14.8712</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0725</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.633</v>
+        <v>-1.6675</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.222</v>
+        <v>-0.1619</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.106</v>
+        <v>-3.7237</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2676</v>
+        <v>-0.1814</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.1548</v>
+        <v>-4.1722</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3207</v>
+        <v>-0.2111</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.3761</v>
+        <v>-4.8553</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3207</v>
+        <v>-0.2111</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.3761</v>
+        <v>-4.8553</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.55</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3112</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
-        <v>30.1576</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.42</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0478</v>
+        <v>1.0317</v>
       </c>
       <c r="J158" t="n">
-        <v>24.0994</v>
+        <v>23.7291</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.31</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8037</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>18.4851</v>
+        <v>18.653</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4756</v>
+        <v>0.5333</v>
       </c>
       <c r="J160" t="n">
-        <v>10.9388</v>
+        <v>12.2659</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.63</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.1063</v>
+        <v>-1.0954</v>
       </c>
       <c r="J161" t="n">
-        <v>-25.4449</v>
+        <v>-25.1942</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.07</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1999</v>
+        <v>0.2003</v>
       </c>
       <c r="J162" t="n">
-        <v>5.5972</v>
+        <v>5.6084</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.06</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1814</v>
+        <v>0.1779</v>
       </c>
       <c r="J163" t="n">
-        <v>5.0792</v>
+        <v>4.9812</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1432</v>
+        <v>-0.094</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.0096</v>
+        <v>-2.632</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2564</v>
+        <v>-0.1595</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.1792</v>
+        <v>-4.466</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4392</v>
+        <v>-0.2806</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.2976</v>
+        <v>-7.8568</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.46</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1789</v>
+        <v>1.1089</v>
       </c>
       <c r="J167" t="n">
-        <v>33.0092</v>
+        <v>31.0492</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7399</v>
+        <v>0.7219</v>
       </c>
       <c r="J168" t="n">
-        <v>20.7172</v>
+        <v>20.2132</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.347</v>
+        <v>0.3727</v>
       </c>
       <c r="J169" t="n">
-        <v>9.715999999999999</v>
+        <v>10.4356</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3135</v>
+        <v>0.3462</v>
       </c>
       <c r="J170" t="n">
-        <v>8.778</v>
+        <v>9.6936</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.68</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.9829</v>
+        <v>-0.956</v>
       </c>
       <c r="J171" t="n">
-        <v>-27.5212</v>
+        <v>-26.768</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4685</v>
+        <v>0.542</v>
       </c>
       <c r="J172" t="n">
-        <v>10.307</v>
+        <v>11.924</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4545</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>9.999000000000001</v>
+        <v>11.4994</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.72</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4564</v>
+        <v>-0.2979</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.0408</v>
+        <v>-6.5538</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.54</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.694</v>
+        <v>-0.4666</v>
       </c>
       <c r="J175" t="n">
-        <v>-15.268</v>
+        <v>-10.2652</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.54</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.694</v>
+        <v>-0.4666</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.268</v>
+        <v>-10.2652</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.73</v>
       </c>
       <c r="I177" t="n">
-        <v>1.6077</v>
+        <v>1.3985</v>
       </c>
       <c r="J177" t="n">
-        <v>35.3694</v>
+        <v>30.767</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9363</v>
+        <v>0.9619</v>
       </c>
       <c r="J178" t="n">
-        <v>20.5986</v>
+        <v>21.1618</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.37</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8908</v>
+        <v>0.9223</v>
       </c>
       <c r="J179" t="n">
-        <v>19.5976</v>
+        <v>20.2906</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.09</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1639</v>
+        <v>0.2485</v>
       </c>
       <c r="J180" t="n">
-        <v>3.6058</v>
+        <v>5.467</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3277</v>
+        <v>-0.2429</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.2094</v>
+        <v>-5.3438</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.02</v>
       </c>
       <c r="I182" t="n">
-        <v>2.0271</v>
+        <v>1.7399</v>
       </c>
       <c r="J182" t="n">
-        <v>44.5962</v>
+        <v>38.2778</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8224</v>
+        <v>0.8589</v>
       </c>
       <c r="J183" t="n">
-        <v>18.0928</v>
+        <v>18.8958</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2747</v>
+        <v>0.361</v>
       </c>
       <c r="J184" t="n">
-        <v>6.0434</v>
+        <v>7.942</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.06</v>
       </c>
       <c r="I185" t="n">
-        <v>0.077</v>
+        <v>0.1592</v>
       </c>
       <c r="J185" t="n">
-        <v>1.694</v>
+        <v>3.5024</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.97</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2926</v>
+        <v>-0.2071</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.4372</v>
+        <v>-4.5562</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.099</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.0746</v>
+        <v>-2.178</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3489</v>
+        <v>-0.2567</v>
       </c>
       <c r="J188" t="n">
-        <v>-7.6758</v>
+        <v>-5.6474</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.75</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3489</v>
+        <v>-0.2567</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.6758</v>
+        <v>-5.6474</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4759</v>
+        <v>-0.321</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.4698</v>
+        <v>-7.062</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5493</v>
+        <v>-0.3679</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.0846</v>
+        <v>-8.0938</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.34</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9089</v>
+        <v>0.9002</v>
       </c>
       <c r="J192" t="n">
-        <v>27.267</v>
+        <v>27.006</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7713</v>
+        <v>0.7605</v>
       </c>
       <c r="J193" t="n">
-        <v>23.139</v>
+        <v>22.815</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5437</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>16.311</v>
+        <v>16.317</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2313</v>
+        <v>0.2847</v>
       </c>
       <c r="J195" t="n">
-        <v>6.939</v>
+        <v>8.541</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.87</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.543</v>
+        <v>-0.4768</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.29</v>
+        <v>-14.304</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3854</v>
+        <v>0.4359</v>
       </c>
       <c r="J197" t="n">
-        <v>11.562</v>
+        <v>13.077</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1742</v>
+        <v>0.1729</v>
       </c>
       <c r="J198" t="n">
-        <v>5.226</v>
+        <v>5.187</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="J199" t="n">
-        <v>2.709</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4012</v>
+        <v>-0.2534</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.036</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4846</v>
+        <v>-0.3118</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.538</v>
+        <v>-9.353999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.84</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1452</v>
+        <v>-0.1404</v>
       </c>
       <c r="J202" t="n">
-        <v>-2.904</v>
+        <v>-2.808</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.66</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.4335</v>
+        <v>-0.3265</v>
       </c>
       <c r="J203" t="n">
-        <v>-8.67</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.65</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4523</v>
+        <v>-0.3354</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.045999999999999</v>
+        <v>-6.708</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.54</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6387</v>
+        <v>-0.4353</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.774</v>
+        <v>-8.706</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.52</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6669</v>
+        <v>-0.454</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.338</v>
+        <v>-9.08</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.84</v>
       </c>
       <c r="I207" t="n">
-        <v>1.7404</v>
+        <v>1.4933</v>
       </c>
       <c r="J207" t="n">
-        <v>34.808</v>
+        <v>29.866</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.57</v>
       </c>
       <c r="I208" t="n">
-        <v>1.2404</v>
+        <v>1.1805</v>
       </c>
       <c r="J208" t="n">
-        <v>24.808</v>
+        <v>23.61</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9434</v>
+        <v>1.0242</v>
       </c>
       <c r="J209" t="n">
-        <v>18.868</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.31</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6503</v>
+        <v>0.7679</v>
       </c>
       <c r="J210" t="n">
-        <v>13.006</v>
+        <v>15.358</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.11</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1758</v>
+        <v>0.2734</v>
       </c>
       <c r="J211" t="n">
-        <v>3.516</v>
+        <v>5.468</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.51</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.9835</v>
       </c>
       <c r="J212" t="n">
-        <v>23.694</v>
+        <v>29.505</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1116</v>
+        <v>0.1005</v>
       </c>
       <c r="J213" t="n">
-        <v>3.348</v>
+        <v>3.015</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.99</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0174</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.264</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.66</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5642</v>
+        <v>-0.3691</v>
       </c>
       <c r="J215" t="n">
-        <v>-16.926</v>
+        <v>-11.073</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6395</v>
+        <v>-0.4247</v>
       </c>
       <c r="J216" t="n">
-        <v>-19.185</v>
+        <v>-12.741</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.35</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9182</v>
+        <v>0.9143</v>
       </c>
       <c r="J217" t="n">
-        <v>27.546</v>
+        <v>27.429</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.22</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6071</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>18.213</v>
+        <v>18.342</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6071</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>18.213</v>
+        <v>18.342</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.14</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3639</v>
+        <v>0.4157</v>
       </c>
       <c r="J220" t="n">
-        <v>10.917</v>
+        <v>12.471</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.96</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.288</v>
+        <v>-0.2114</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.640000000000001</v>
+        <v>-6.342</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2</v>
       </c>
       <c r="I222" t="n">
-        <v>2.0351</v>
+        <v>1.7538</v>
       </c>
       <c r="J222" t="n">
-        <v>50.8775</v>
+        <v>43.845</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4886</v>
+        <v>0.536</v>
       </c>
       <c r="J223" t="n">
-        <v>12.215</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.17</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4313</v>
+        <v>0.487</v>
       </c>
       <c r="J224" t="n">
-        <v>10.7825</v>
+        <v>12.175</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.84</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6339</v>
+        <v>-0.571</v>
       </c>
       <c r="J225" t="n">
-        <v>-15.8475</v>
+        <v>-14.275</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.82</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.624</v>
       </c>
       <c r="J226" t="n">
-        <v>-17.075</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5102</v>
+        <v>0.5996</v>
       </c>
       <c r="J227" t="n">
-        <v>12.755</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.02</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1064</v>
+        <v>0.0849</v>
       </c>
       <c r="J228" t="n">
-        <v>2.66</v>
+        <v>2.1225</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2821</v>
+        <v>-0.1781</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.0525</v>
+        <v>-4.4525</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.434</v>
+        <v>-0.2781</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.85</v>
+        <v>-6.9525</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5165</v>
+        <v>-0.3357</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.9125</v>
+        <v>-8.3925</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2514</v>
+        <v>1.1568</v>
       </c>
       <c r="J232" t="n">
-        <v>42.5476</v>
+        <v>39.3312</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6056</v>
+        <v>0.5959</v>
       </c>
       <c r="J233" t="n">
-        <v>20.5904</v>
+        <v>20.2606</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2387</v>
+        <v>0.2874</v>
       </c>
       <c r="J234" t="n">
-        <v>8.1158</v>
+        <v>9.771599999999999</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0999</v>
+        <v>-0.0338</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.3966</v>
+        <v>-1.1492</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.91</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4294</v>
+        <v>-0.3593</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.5996</v>
+        <v>-12.2162</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.29</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5258</v>
+        <v>0.6219</v>
       </c>
       <c r="J237" t="n">
-        <v>17.8772</v>
+        <v>21.1446</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.02</v>
       </c>
       <c r="I238" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="J238" t="n">
-        <v>3.1892</v>
+        <v>2.618</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2929</v>
+        <v>-0.1816</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.958600000000001</v>
+        <v>-6.1744</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3846</v>
+        <v>-0.2425</v>
       </c>
       <c r="J240" t="n">
-        <v>-13.0764</v>
+        <v>-8.244999999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3991</v>
+        <v>-0.2525</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.5694</v>
+        <v>-8.585000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.59</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2599</v>
+        <v>1.1986</v>
       </c>
       <c r="J242" t="n">
-        <v>25.198</v>
+        <v>23.972</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.58</v>
       </c>
       <c r="I243" t="n">
-        <v>1.2397</v>
+        <v>1.1869</v>
       </c>
       <c r="J243" t="n">
-        <v>24.794</v>
+        <v>23.738</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I244" t="n">
-        <v>1.1562</v>
+        <v>1.1405</v>
       </c>
       <c r="J244" t="n">
-        <v>23.124</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.48</v>
       </c>
       <c r="I245" t="n">
-        <v>1.0077</v>
+        <v>1.0714</v>
       </c>
       <c r="J245" t="n">
-        <v>20.154</v>
+        <v>21.428</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.29</v>
       </c>
       <c r="I246" t="n">
-        <v>0.5913</v>
+        <v>0.7141</v>
       </c>
       <c r="J246" t="n">
-        <v>11.826</v>
+        <v>14.282</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2071</v>
+        <v>-0.1872</v>
       </c>
       <c r="J247" t="n">
-        <v>-4.142</v>
+        <v>-3.744</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.74</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2689</v>
+        <v>-0.2312</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.378</v>
+        <v>-4.624</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.53</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.6249</v>
+        <v>-0.4335</v>
       </c>
       <c r="J249" t="n">
-        <v>-12.498</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.43</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.7691</v>
+        <v>-0.5278</v>
       </c>
       <c r="J250" t="n">
-        <v>-15.382</v>
+        <v>-10.556</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.43</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7691</v>
+        <v>-0.5278</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.382</v>
+        <v>-10.556</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.3</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7942</v>
+        <v>0.7946</v>
       </c>
       <c r="J252" t="n">
-        <v>20.6492</v>
+        <v>20.6596</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.3</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7942</v>
+        <v>0.7946</v>
       </c>
       <c r="J253" t="n">
-        <v>20.6492</v>
+        <v>20.6596</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.25</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6724</v>
+        <v>0.6784</v>
       </c>
       <c r="J254" t="n">
-        <v>17.4824</v>
+        <v>17.6384</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3241</v>
+        <v>0.3856</v>
       </c>
       <c r="J255" t="n">
-        <v>8.426600000000001</v>
+        <v>10.0256</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1218</v>
+        <v>-0.0476</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.1668</v>
+        <v>-1.2376</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.13</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2997</v>
+        <v>0.3247</v>
       </c>
       <c r="J257" t="n">
-        <v>7.7922</v>
+        <v>8.4422</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.12</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2837</v>
+        <v>0.3045</v>
       </c>
       <c r="J258" t="n">
-        <v>7.3762</v>
+        <v>7.917</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1213</v>
+        <v>-0.0829</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.1538</v>
+        <v>-2.1554</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.93</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1461</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.7986</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.58</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6611</v>
+        <v>-0.4411</v>
       </c>
       <c r="J261" t="n">
-        <v>-17.1886</v>
+        <v>-11.4686</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4926/event_4926_evp_summary.xlsx
+++ b/database/event/4926/event_4926_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0647</v>
+        <v>6.3003</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2695</v>
+        <v>2.3576</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0999</v>
+        <v>2.2438</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0647</v>
+        <v>6.3003</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7258</v>
+        <v>2.6726</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3389</v>
+        <v>3.6277</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1179</v>
+        <v>3.9238</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1411</v>
+        <v>2.1188</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3389</v>
+        <v>3.6277</v>
       </c>
       <c r="K2" t="n">
         <v>86</v>
@@ -529,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>5.48</v>
+        <v>5.746499999999999</v>
       </c>
       <c r="N2" t="n">
         <v>246</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8456</v>
+        <v>5.8401</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1875</v>
+        <v>2.1854</v>
       </c>
       <c r="D3" t="n">
-        <v>2.001</v>
+        <v>2.0343</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8456</v>
+        <v>5.8401</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8128</v>
+        <v>2.7317</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0328</v>
+        <v>3.1084</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4242</v>
+        <v>4.1188</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3004</v>
+        <v>2.2241</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0328</v>
+        <v>3.1084</v>
       </c>
       <c r="K3" t="n">
         <v>86</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3332</v>
+        <v>5.3325</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4559</v>
+        <v>5.4928</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0416</v>
+        <v>2.0554</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8251</v>
+        <v>1.8762</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4559</v>
+        <v>5.4928</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9643</v>
+        <v>2.8902</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4916</v>
+        <v>2.6026</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9579</v>
+        <v>4.6416</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5779</v>
+        <v>2.5064</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4916</v>
+        <v>2.6026</v>
       </c>
       <c r="K4" t="n">
         <v>70</v>
@@ -621,7 +621,7 @@
         <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0695</v>
+        <v>5.109</v>
       </c>
       <c r="N4" t="n">
         <v>225</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0552</v>
+        <v>4.0974</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5175</v>
+        <v>1.5333</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1927</v>
+        <v>1.241</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0552</v>
+        <v>4.0974</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2908</v>
+        <v>3.2318</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7644</v>
+        <v>0.8656</v>
       </c>
       <c r="H5" t="n">
-        <v>6.1084</v>
+        <v>5.7686</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1761</v>
+        <v>3.115</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7644</v>
+        <v>0.8656</v>
       </c>
       <c r="K5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9405</v>
+        <v>3.9806</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9537</v>
+        <v>4.0014</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4795</v>
+        <v>1.4974</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1469</v>
+        <v>1.1973</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9537</v>
+        <v>4.0014</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9725</v>
+        <v>1.8573</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9812</v>
+        <v>2.1441</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9725</v>
+        <v>1.8573</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0256</v>
+        <v>1.0029</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9812</v>
+        <v>2.1441</v>
       </c>
       <c r="K6" t="n">
         <v>86</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0068</v>
+        <v>3.147</v>
       </c>
       <c r="N6" t="n">
         <v>246</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4911</v>
+        <v>3.4448</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3064</v>
+        <v>1.2891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9439</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4911</v>
+        <v>3.4448</v>
       </c>
       <c r="F7" t="n">
-        <v>2.991</v>
+        <v>2.9182</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5001</v>
+        <v>0.5266</v>
       </c>
       <c r="H7" t="n">
-        <v>5.052</v>
+        <v>4.734</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6268</v>
+        <v>2.5563</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5001</v>
+        <v>0.5266</v>
       </c>
       <c r="K7" t="n">
         <v>70</v>
@@ -759,7 +759,7 @@
         <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1269</v>
+        <v>3.0829</v>
       </c>
       <c r="N7" t="n">
         <v>225</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0302</v>
+        <v>3.0117</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1339</v>
+        <v>1.127</v>
       </c>
       <c r="D8" t="n">
-        <v>0.73</v>
+        <v>0.7468</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0302</v>
+        <v>3.0117</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3231</v>
+        <v>3.2383</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2929</v>
+        <v>-0.2266</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2223</v>
+        <v>5.7901</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2353</v>
+        <v>3.1266</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2929</v>
+        <v>-0.2266</v>
       </c>
       <c r="K8" t="n">
         <v>70</v>
@@ -805,7 +805,7 @@
         <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9424</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
         <v>225</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7514</v>
+        <v>2.9467</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0296</v>
+        <v>1.1027</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6041</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7514</v>
+        <v>2.9467</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6153</v>
+        <v>0.3945</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1361</v>
+        <v>2.5522</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7284</v>
+        <v>0.3945</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9386</v>
+        <v>0.213</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1361</v>
+        <v>2.5522</v>
       </c>
       <c r="K9" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="L9" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0747</v>
+        <v>2.7652</v>
       </c>
       <c r="N9" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6237</v>
+        <v>2.6066</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9818</v>
+        <v>0.9754</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5465</v>
+        <v>0.5624</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6237</v>
+        <v>2.6066</v>
       </c>
       <c r="F10" t="n">
-        <v>0.33</v>
+        <v>2.5118</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2937</v>
+        <v>0.0948</v>
       </c>
       <c r="H10" t="n">
-        <v>0.33</v>
+        <v>3.3932</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1716</v>
+        <v>1.8323</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2937</v>
+        <v>0.0948</v>
       </c>
       <c r="K10" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="L10" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4653</v>
+        <v>1.9271</v>
       </c>
       <c r="N10" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5655</v>
+        <v>2.4775</v>
       </c>
       <c r="C11" t="n">
-        <v>0.96</v>
+        <v>0.9271</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5202</v>
+        <v>0.5036</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5655</v>
+        <v>2.4775</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0879</v>
+        <v>1.9521</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4776</v>
+        <v>0.5254</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0879</v>
+        <v>1.9521</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0856</v>
+        <v>1.0541</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4776</v>
+        <v>0.5254</v>
       </c>
       <c r="K11" t="n">
         <v>131</v>
@@ -943,7 +943,7 @@
         <v>70</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5632</v>
+        <v>1.5795</v>
       </c>
       <c r="N11" t="n">
         <v>201</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2744</v>
+        <v>2.1189</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8511</v>
+        <v>0.7929</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3888</v>
+        <v>0.3404</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2744</v>
+        <v>2.1189</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2744</v>
+        <v>2.1189</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2744</v>
+        <v>2.1189</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2744</v>
+        <v>2.1189</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2744</v>
+        <v>2.1189</v>
       </c>
       <c r="N12" t="n">
         <v>131</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2669</v>
+        <v>2.0757</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3854</v>
+        <v>0.3207</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2669</v>
+        <v>2.0757</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1681</v>
+        <v>2.0017</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0988</v>
+        <v>0.074</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1681</v>
+        <v>2.0017</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1273</v>
+        <v>1.0809</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0988</v>
+        <v>0.074</v>
       </c>
       <c r="K13" t="n">
         <v>161</v>
@@ -1035,7 +1035,7 @@
         <v>75</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2261</v>
+        <v>1.1549</v>
       </c>
       <c r="N13" t="n">
         <v>236</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1642</v>
+        <v>2.0514</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8099</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.339</v>
+        <v>0.3096</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1642</v>
+        <v>2.0514</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1642</v>
+        <v>2.0514</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1642</v>
+        <v>2.0514</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1642</v>
+        <v>2.0514</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1642</v>
+        <v>2.0514</v>
       </c>
       <c r="N14" t="n">
         <v>131</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1039</v>
+        <v>2.0344</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7873</v>
+        <v>0.7613</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3118</v>
+        <v>0.3019</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1039</v>
+        <v>2.0344</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6567</v>
+        <v>1.5371</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4472</v>
+        <v>0.4973</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6567</v>
+        <v>1.5371</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4472</v>
+        <v>0.4973</v>
       </c>
       <c r="K15" t="n">
         <v>131</v>
@@ -1127,7 +1127,7 @@
         <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3086</v>
+        <v>1.3273</v>
       </c>
       <c r="N15" t="n">
         <v>201</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9349</v>
+        <v>1.8651</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7241</v>
+        <v>0.6979</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2355</v>
+        <v>0.2248</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9349</v>
+        <v>1.8651</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4482</v>
+        <v>1.9458</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5133</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1397</v>
+        <v>1.9458</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6325</v>
+        <v>1.0507</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5133</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>131</v>
@@ -1173,7 +1173,7 @@
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1192</v>
+        <v>0.97</v>
       </c>
       <c r="N16" t="n">
         <v>201</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9306</v>
+        <v>1.8302</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7224</v>
+        <v>0.6849</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2336</v>
+        <v>0.2089</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9306</v>
+        <v>1.8302</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0604</v>
+        <v>2.3585</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1298</v>
+        <v>-0.5283</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0604</v>
+        <v>2.8873</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0713</v>
+        <v>1.5591</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1298</v>
+        <v>-0.5283</v>
       </c>
       <c r="K17" t="n">
         <v>131</v>
@@ -1219,7 +1219,7 @@
         <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9414999999999999</v>
+        <v>1.0308</v>
       </c>
       <c r="N17" t="n">
         <v>201</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8261</v>
+        <v>1.7236</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6833</v>
+        <v>0.645</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1864</v>
+        <v>0.1604</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8261</v>
+        <v>1.7236</v>
       </c>
       <c r="F18" t="n">
-        <v>1.855</v>
+        <v>1.5961</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0289</v>
+        <v>0.1275</v>
       </c>
       <c r="H18" t="n">
-        <v>1.855</v>
+        <v>1.5961</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9645</v>
+        <v>0.8619</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0289</v>
+        <v>0.1275</v>
       </c>
       <c r="K18" t="n">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="L18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9356</v>
+        <v>0.9894000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>236</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5829</v>
+        <v>1.683</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5923</v>
+        <v>0.6298</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0766</v>
+        <v>0.1419</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5829</v>
+        <v>1.683</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7938</v>
+        <v>1.6935</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2109</v>
+        <v>-0.0105</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7938</v>
+        <v>1.6935</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9327</v>
+        <v>0.9145</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2109</v>
+        <v>-0.0105</v>
       </c>
       <c r="K19" t="n">
         <v>86</v>
@@ -1311,7 +1311,7 @@
         <v>160</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7218</v>
+        <v>0.904</v>
       </c>
       <c r="N19" t="n">
         <v>246</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5783</v>
+        <v>1.6777</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5906</v>
+        <v>0.6278</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0745</v>
+        <v>0.1395</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5783</v>
+        <v>1.6777</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4582</v>
+        <v>1.7269</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1201</v>
+        <v>-0.0492</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4582</v>
+        <v>1.7269</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7582</v>
+        <v>0.9325</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1201</v>
+        <v>-0.0492</v>
       </c>
       <c r="K20" t="n">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="L20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8783</v>
+        <v>0.8833</v>
       </c>
       <c r="N20" t="n">
-        <v>201</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4707</v>
+        <v>1.3508</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5503</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0259</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4707</v>
+        <v>1.3508</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4707</v>
+        <v>1.3508</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4707</v>
+        <v>1.3508</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4707</v>
+        <v>1.3508</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4707</v>
+        <v>1.3508</v>
       </c>
       <c r="N21" t="n">
         <v>155</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1759</v>
+        <v>1.1839</v>
       </c>
       <c r="C22" t="n">
-        <v>0.44</v>
+        <v>0.443</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1072</v>
+        <v>-0.0853</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1759</v>
+        <v>1.1839</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1759</v>
+        <v>1.1839</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1759</v>
+        <v>1.1839</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1759</v>
+        <v>1.1839</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1759</v>
+        <v>1.1839</v>
       </c>
       <c r="N22" t="n">
         <v>155</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0182</v>
+        <v>0.9845</v>
       </c>
       <c r="C23" t="n">
-        <v>0.381</v>
+        <v>0.3684</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1783</v>
+        <v>-0.176</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0182</v>
+        <v>0.9845</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0182</v>
+        <v>0.9845</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0182</v>
+        <v>0.9845</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0182</v>
+        <v>0.9845</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0182</v>
+        <v>0.9845</v>
       </c>
       <c r="N23" t="n">
         <v>155</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7138</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2816</v>
+        <v>0.2671</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2983</v>
+        <v>-0.2993</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7138</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7138</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7138</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7138</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7138</v>
       </c>
       <c r="N24" t="n">
         <v>76</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6879</v>
+        <v>0.6567</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2574</v>
+        <v>0.2457</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3275</v>
+        <v>-0.3253</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6879</v>
+        <v>0.6567</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6879</v>
+        <v>0.6567</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6879</v>
+        <v>0.6567</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6879</v>
+        <v>0.6567</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6879</v>
+        <v>0.6567</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6482</v>
+        <v>0.6476</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2426</v>
+        <v>0.2423</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3454</v>
+        <v>-0.3294</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6482</v>
+        <v>0.6476</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6482</v>
+        <v>0.6476</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6482</v>
+        <v>0.6476</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6482</v>
+        <v>0.6476</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6482</v>
+        <v>0.6476</v>
       </c>
       <c r="N26" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3786</v>
+        <v>0.5027</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1417</v>
+        <v>0.1881</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4671</v>
+        <v>-0.3954</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3786</v>
+        <v>0.5027</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4926</v>
+        <v>1.4608</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.114</v>
+        <v>-0.9581</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4926</v>
+        <v>1.4608</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7761</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.114</v>
+        <v>-0.9581</v>
       </c>
       <c r="K27" t="n">
         <v>70</v>
@@ -1679,7 +1679,7 @@
         <v>155</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3379000000000001</v>
+        <v>-0.1693</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3642</v>
+        <v>0.2826</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1363</v>
+        <v>0.1058</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4736</v>
+        <v>-0.4956</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3642</v>
+        <v>0.2826</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3642</v>
+        <v>0.2826</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3642</v>
+        <v>0.2826</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3642</v>
+        <v>0.2826</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3642</v>
+        <v>0.2826</v>
       </c>
       <c r="N28" t="n">
         <v>131</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Luken</t>
+          <t>leo_drk</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2344</v>
+        <v>0.185</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0877</v>
+        <v>0.0692</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5322</v>
+        <v>-0.54</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2344</v>
+        <v>0.185</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2344</v>
+        <v>0.185</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2344</v>
+        <v>0.185</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2344</v>
+        <v>0.185</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2344</v>
+        <v>0.185</v>
       </c>
       <c r="N29" t="n">
         <v>86</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>leo_drk</t>
+          <t>Luken</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2222</v>
+        <v>0.1817</v>
       </c>
       <c r="C30" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5377</v>
+        <v>-0.5415</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2222</v>
+        <v>0.1817</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2222</v>
+        <v>0.1817</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2222</v>
+        <v>0.1817</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2222</v>
+        <v>0.1817</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2222</v>
+        <v>0.1817</v>
       </c>
       <c r="N30" t="n">
         <v>86</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0378</v>
+        <v>-0.0619</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0141</v>
+        <v>-0.0232</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6551</v>
+        <v>-0.6524</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0378</v>
+        <v>-0.0619</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0378</v>
+        <v>-0.0619</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0378</v>
+        <v>-0.0619</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0378</v>
+        <v>-0.0619</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0378</v>
+        <v>-0.0619</v>
       </c>
       <c r="N31" t="n">
         <v>86</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0674</v>
+        <v>-0.1001</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0252</v>
+        <v>-0.0375</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6684</v>
+        <v>-0.6698</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0674</v>
+        <v>-0.1001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0674</v>
+        <v>-0.1001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0674</v>
+        <v>-0.1001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0674</v>
+        <v>-0.1001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0674</v>
+        <v>-0.1001</v>
       </c>
       <c r="N32" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0273</v>
+        <v>-0.0375</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.6698</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="N33" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1784</v>
+        <v>-0.1965</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0668</v>
+        <v>-0.0735</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7186</v>
+        <v>-0.7137</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1784</v>
+        <v>-0.1965</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1784</v>
+        <v>-0.1965</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1784</v>
+        <v>-0.1965</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1784</v>
+        <v>-0.1965</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1784</v>
+        <v>-0.1965</v>
       </c>
       <c r="N34" t="n">
         <v>86</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.2143</v>
+        <v>-0.2393</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0895</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7348</v>
+        <v>-0.7331</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2143</v>
+        <v>-0.2393</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2143</v>
+        <v>-0.2393</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2143</v>
+        <v>-0.2393</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2143</v>
+        <v>-0.2393</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.2143</v>
+        <v>-0.2393</v>
       </c>
       <c r="N35" t="n">
         <v>76</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3669</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1307</v>
+        <v>-0.1373</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7957</v>
+        <v>-0.7912</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3669</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3669</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3669</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3669</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3669</v>
       </c>
       <c r="N36" t="n">
         <v>76</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3521</v>
+        <v>-0.3952</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1318</v>
+        <v>-0.1479</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.797</v>
+        <v>-0.8041</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.3521</v>
+        <v>-0.3952</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3521</v>
+        <v>-0.3952</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3521</v>
+        <v>-0.3952</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3521</v>
+        <v>-0.3952</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.3521</v>
+        <v>-0.3952</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.4055</v>
+        <v>-0.5013</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1517</v>
+        <v>-0.1876</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.8524</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.4055</v>
+        <v>-0.5013</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5945</v>
+        <v>0.4987</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5945</v>
+        <v>0.4987</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3091</v>
+        <v>0.2693</v>
       </c>
       <c r="J38" t="n">
         <v>-1</v>
@@ -2185,7 +2185,7 @@
         <v>75</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6909000000000001</v>
+        <v>-0.7307</v>
       </c>
       <c r="N38" t="n">
         <v>236</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1883</v>
+        <v>-1.2201</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4447</v>
+        <v>-0.4566</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1745</v>
+        <v>-1.1796</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1883</v>
+        <v>-1.2201</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1883</v>
+        <v>-1.2201</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1883</v>
+        <v>-1.2201</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1883</v>
+        <v>-1.2201</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1883</v>
+        <v>-1.2201</v>
       </c>
       <c r="N39" t="n">
         <v>76</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3601</v>
+        <v>-1.3814</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.509</v>
+        <v>-0.5169</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.252</v>
+        <v>-1.253</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3601</v>
+        <v>-1.3814</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8691</v>
+        <v>-0.9072</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.491</v>
+        <v>-0.4742</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8691</v>
+        <v>-0.9072</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4519</v>
+        <v>-0.4899</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.491</v>
+        <v>-0.4742</v>
       </c>
       <c r="K40" t="n">
         <v>161</v>
@@ -2277,7 +2277,7 @@
         <v>75</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9429000000000001</v>
+        <v>-0.9641</v>
       </c>
       <c r="N40" t="n">
         <v>236</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9104</v>
+        <v>-1.8127</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7149</v>
+        <v>-0.6783</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5005</v>
+        <v>-1.4494</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9104</v>
+        <v>-1.8127</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9104</v>
+        <v>-1.8127</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9104</v>
+        <v>-1.8127</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9104</v>
+        <v>-1.8127</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9104</v>
+        <v>-1.8127</v>
       </c>
       <c r="N41" t="n">
         <v>131</v>
@@ -2429,10 +2429,10 @@
         <v>1.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1541</v>
+        <v>0.1644</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2394</v>
+        <v>5.5896</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1043</v>
+        <v>0.1141</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5462</v>
+        <v>3.8794</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1043</v>
+        <v>0.1141</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5462</v>
+        <v>3.8794</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.99</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0218</v>
+        <v>-0.0262</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7412</v>
+        <v>-0.8908</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1248</v>
+        <v>-0.1368</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.2432</v>
+        <v>-4.6512</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.64</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8122</v>
+        <v>0.794</v>
       </c>
       <c r="J7" t="n">
-        <v>27.6148</v>
+        <v>26.996</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2062</v>
+        <v>0.2211</v>
       </c>
       <c r="J8" t="n">
-        <v>7.0108</v>
+        <v>7.5174</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1074</v>
+        <v>0.1207</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6516</v>
+        <v>4.1038</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.196</v>
+        <v>-0.2078</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.664</v>
+        <v>-7.0652</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3627</v>
+        <v>-0.3719</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.3318</v>
+        <v>-12.6446</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3092</v>
+        <v>1.3747</v>
       </c>
       <c r="J12" t="n">
-        <v>35.3484</v>
+        <v>37.1169</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7994</v>
+        <v>0.7528</v>
       </c>
       <c r="J13" t="n">
-        <v>21.5838</v>
+        <v>20.3256</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3218</v>
+        <v>0.3234</v>
       </c>
       <c r="J14" t="n">
-        <v>8.688599999999999</v>
+        <v>8.7318</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4371</v>
+        <v>-0.4159</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.8017</v>
+        <v>-11.2293</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.67</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9762</v>
+        <v>-0.8932</v>
       </c>
       <c r="J16" t="n">
-        <v>-26.3574</v>
+        <v>-24.1164</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2641</v>
+        <v>0.2653</v>
       </c>
       <c r="J17" t="n">
-        <v>7.1307</v>
+        <v>7.1631</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0152</v>
+        <v>-0.0212</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4104</v>
+        <v>-0.5724</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0152</v>
+        <v>-0.0212</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4104</v>
+        <v>-0.5724</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0584</v>
+        <v>-0.0689</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5768</v>
+        <v>-1.8603</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3761</v>
+        <v>-0.3875</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.1547</v>
+        <v>-10.4625</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.89</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5967</v>
+        <v>1.7296</v>
       </c>
       <c r="J22" t="n">
-        <v>38.3208</v>
+        <v>41.5104</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9079</v>
+        <v>0.8572</v>
       </c>
       <c r="J23" t="n">
-        <v>21.7896</v>
+        <v>20.5728</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6877</v>
+        <v>0.6622</v>
       </c>
       <c r="J24" t="n">
-        <v>16.5048</v>
+        <v>15.8928</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1334</v>
+        <v>0.1563</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2016</v>
+        <v>3.7512</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6147</v>
+        <v>-0.5681</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.7528</v>
+        <v>-13.6344</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5736</v>
+        <v>0.5498</v>
       </c>
       <c r="J27" t="n">
-        <v>13.7664</v>
+        <v>13.1952</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0915</v>
+        <v>0.0917</v>
       </c>
       <c r="J28" t="n">
-        <v>2.196</v>
+        <v>2.2008</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0091</v>
+        <v>-0.0165</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2184</v>
+        <v>-0.396</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.89</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1343</v>
+        <v>-0.1498</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.2232</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.32</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6694</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.0656</v>
+        <v>-15.9552</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.02</v>
       </c>
       <c r="I32" t="n">
-        <v>0.112</v>
+        <v>0.1034</v>
       </c>
       <c r="J32" t="n">
-        <v>2.464</v>
+        <v>2.2748</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.92</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0796</v>
+        <v>-0.0989</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.7512</v>
+        <v>-2.1758</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1036</v>
+        <v>-0.1233</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.2792</v>
+        <v>-2.7126</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3803</v>
+        <v>-0.3957</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.3666</v>
+        <v>-8.705399999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.35</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6302</v>
+        <v>-0.6301</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.8644</v>
+        <v>-13.8622</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.54</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5141</v>
+        <v>0.591</v>
       </c>
       <c r="J37" t="n">
-        <v>11.3102</v>
+        <v>13.002</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.45</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4585</v>
+        <v>0.5254</v>
       </c>
       <c r="J38" t="n">
-        <v>10.087</v>
+        <v>11.5588</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.42</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4398</v>
+        <v>0.5031</v>
       </c>
       <c r="J39" t="n">
-        <v>9.675599999999999</v>
+        <v>11.0682</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3706</v>
+        <v>0.4128</v>
       </c>
       <c r="J40" t="n">
-        <v>8.1532</v>
+        <v>9.0816</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0246</v>
+        <v>0.0435</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5412</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8689</v>
+        <v>0.9629</v>
       </c>
       <c r="J42" t="n">
-        <v>19.1158</v>
+        <v>21.1838</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.51</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8565</v>
+        <v>0.9495</v>
       </c>
       <c r="J43" t="n">
-        <v>18.843</v>
+        <v>20.889</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.38</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6933</v>
+        <v>0.7723</v>
       </c>
       <c r="J44" t="n">
-        <v>15.2526</v>
+        <v>16.9906</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.19</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4402</v>
+        <v>0.4903</v>
       </c>
       <c r="J45" t="n">
-        <v>9.6844</v>
+        <v>10.7866</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.96</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2438</v>
+        <v>-0.2242</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.3636</v>
+        <v>-4.9324</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.87</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1345</v>
+        <v>-0.1553</v>
       </c>
       <c r="J47" t="n">
-        <v>-2.959</v>
+        <v>-3.4166</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.84</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1673</v>
+        <v>-0.1881</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.6806</v>
+        <v>-4.1382</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.77</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2384</v>
+        <v>-0.2583</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.2448</v>
+        <v>-5.6826</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3029</v>
+        <v>-0.3216</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.6638</v>
+        <v>-7.0752</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4433</v>
+        <v>-0.4558</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.752599999999999</v>
+        <v>-10.0276</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.35</v>
       </c>
       <c r="I52" t="n">
-        <v>0.695</v>
+        <v>0.7651</v>
       </c>
       <c r="J52" t="n">
-        <v>18.07</v>
+        <v>19.8926</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.26</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5687</v>
+        <v>0.6268</v>
       </c>
       <c r="J53" t="n">
-        <v>14.7862</v>
+        <v>16.2968</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5687</v>
+        <v>0.6268</v>
       </c>
       <c r="J54" t="n">
-        <v>14.7862</v>
+        <v>16.2968</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2866</v>
+        <v>-0.278</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.4516</v>
+        <v>-7.228</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9486</v>
+        <v>-0.8698</v>
       </c>
       <c r="J56" t="n">
-        <v>-24.6636</v>
+        <v>-22.6148</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3407</v>
+        <v>0.3439</v>
       </c>
       <c r="J57" t="n">
-        <v>8.8582</v>
+        <v>8.9414</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.156</v>
+        <v>0.16</v>
       </c>
       <c r="J58" t="n">
-        <v>4.056</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.116</v>
+        <v>-0.13</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.016</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2006</v>
+        <v>-0.2159</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.2156</v>
+        <v>-5.6134</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2995</v>
+        <v>-0.3135</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.787</v>
+        <v>-8.151</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.42</v>
       </c>
       <c r="I62" t="n">
-        <v>0.748</v>
+        <v>0.8312</v>
       </c>
       <c r="J62" t="n">
-        <v>17.952</v>
+        <v>19.9488</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6969</v>
+        <v>0.7754</v>
       </c>
       <c r="J63" t="n">
-        <v>16.7256</v>
+        <v>18.6096</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.32</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6902</v>
       </c>
       <c r="J64" t="n">
-        <v>14.868</v>
+        <v>16.5648</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.19</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4435</v>
+        <v>0.4932</v>
       </c>
       <c r="J65" t="n">
-        <v>10.644</v>
+        <v>11.8368</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3337</v>
+        <v>0.3474</v>
       </c>
       <c r="J66" t="n">
-        <v>8.008800000000001</v>
+        <v>8.3376</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.08</v>
       </c>
       <c r="I67" t="n">
-        <v>0.296</v>
+        <v>0.2793</v>
       </c>
       <c r="J67" t="n">
-        <v>7.104</v>
+        <v>6.7032</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0805</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.932</v>
+        <v>-2.3904</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2588</v>
+        <v>-0.278</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.2112</v>
+        <v>-6.672</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.437</v>
+        <v>-0.4494</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.488</v>
+        <v>-10.7856</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.52</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4742</v>
+        <v>-0.4845</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.3808</v>
+        <v>-11.628</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4004</v>
+        <v>0.4403</v>
       </c>
       <c r="J72" t="n">
-        <v>11.6116</v>
+        <v>12.7687</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.18</v>
       </c>
       <c r="I73" t="n">
-        <v>0.308</v>
+        <v>0.3135</v>
       </c>
       <c r="J73" t="n">
-        <v>8.932</v>
+        <v>9.0915</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1736</v>
+        <v>0.1828</v>
       </c>
       <c r="J74" t="n">
-        <v>5.0344</v>
+        <v>5.3012</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.73</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3072</v>
+        <v>-0.3195</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.908799999999999</v>
+        <v>-9.265499999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.7</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3358</v>
+        <v>-0.3473</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.738200000000001</v>
+        <v>-10.0717</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3809</v>
+        <v>0.4229</v>
       </c>
       <c r="J77" t="n">
-        <v>11.0461</v>
+        <v>12.2641</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3038</v>
+        <v>0.3185</v>
       </c>
       <c r="J78" t="n">
-        <v>8.8102</v>
+        <v>9.236499999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2405</v>
+        <v>0.2564</v>
       </c>
       <c r="J79" t="n">
-        <v>6.9745</v>
+        <v>7.4356</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.98</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0469</v>
+        <v>-0.0511</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.3601</v>
+        <v>-1.4819</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1352</v>
+        <v>-0.1448</v>
       </c>
       <c r="J81" t="n">
-        <v>-3.9208</v>
+        <v>-4.1992</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.48</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.9004</v>
       </c>
       <c r="J82" t="n">
-        <v>17.798</v>
+        <v>19.8088</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>0.711</v>
+        <v>0.7935</v>
       </c>
       <c r="J83" t="n">
-        <v>15.642</v>
+        <v>17.457</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.39</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6988</v>
+        <v>0.78</v>
       </c>
       <c r="J84" t="n">
-        <v>15.3736</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6747</v>
+        <v>0.7533</v>
       </c>
       <c r="J85" t="n">
-        <v>14.8434</v>
+        <v>16.5726</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.25</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5174</v>
+        <v>0.5789</v>
       </c>
       <c r="J86" t="n">
-        <v>11.3828</v>
+        <v>12.7358</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.97</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0106</v>
+        <v>-0.0276</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.2332</v>
+        <v>-0.6072</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.89</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.113</v>
+        <v>-0.1334</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.486</v>
+        <v>-2.9348</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1245</v>
+        <v>-0.1449</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.739</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4349</v>
+        <v>-0.4477</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.5678</v>
+        <v>-9.849399999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.46</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5278</v>
+        <v>-0.535</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.6116</v>
+        <v>-11.77</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.95</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6466</v>
+        <v>1.6448</v>
       </c>
       <c r="J92" t="n">
-        <v>41.165</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.27</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6986</v>
+        <v>0.6744</v>
       </c>
       <c r="J93" t="n">
-        <v>17.465</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.26</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6755</v>
+        <v>0.6539</v>
       </c>
       <c r="J94" t="n">
-        <v>16.8875</v>
+        <v>16.3475</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.24</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6287</v>
+        <v>0.6123</v>
       </c>
       <c r="J95" t="n">
-        <v>15.7175</v>
+        <v>15.3075</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0828</v>
+        <v>-0.0575</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.07</v>
+        <v>-1.4375</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.29</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7113</v>
+        <v>0.6642</v>
       </c>
       <c r="J97" t="n">
-        <v>17.7825</v>
+        <v>16.605</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1208</v>
+        <v>-0.1395</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.02</v>
+        <v>-3.4875</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.74</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2711</v>
+        <v>-0.2895</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.7775</v>
+        <v>-7.2375</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.62</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3845</v>
+        <v>-0.3989</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.612500000000001</v>
+        <v>-9.9725</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.41</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5786</v>
+        <v>-0.5817</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.465</v>
+        <v>-14.5425</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.24</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6775</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>19.6475</v>
+        <v>18.7253</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.22</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6022</v>
       </c>
       <c r="J103" t="n">
-        <v>18.2265</v>
+        <v>17.4638</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6022</v>
       </c>
       <c r="J104" t="n">
-        <v>18.2265</v>
+        <v>17.4638</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="J105" t="n">
-        <v>2.0039</v>
+        <v>2.4012</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.87</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4661</v>
+        <v>-0.4421</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.5169</v>
+        <v>-12.8209</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>17.6146</v>
+        <v>16.8519</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0261</v>
+        <v>-0.0352</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.7569</v>
+        <v>-1.0208</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.88</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1452</v>
+        <v>-0.1609</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.2108</v>
+        <v>-4.6661</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2663</v>
+        <v>-0.2818</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.7227</v>
+        <v>-8.1722</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4087</v>
+        <v>-0.4195</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.8523</v>
+        <v>-12.1655</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.16</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3006</v>
+        <v>0.3017</v>
       </c>
       <c r="J112" t="n">
-        <v>8.116199999999999</v>
+        <v>8.145899999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.96</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0561</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.5147</v>
+        <v>-1.8117</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1039</v>
+        <v>-0.1177</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.8053</v>
+        <v>-3.1779</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.86</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1678</v>
+        <v>-0.1834</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.5306</v>
+        <v>-4.9518</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3452</v>
+        <v>-0.3582</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.320399999999999</v>
+        <v>-9.6714</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4762</v>
+        <v>0.4872</v>
       </c>
       <c r="J117" t="n">
-        <v>12.8574</v>
+        <v>13.1544</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.3</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3967</v>
+        <v>0.4113</v>
       </c>
       <c r="J118" t="n">
-        <v>10.7109</v>
+        <v>11.1051</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3039</v>
+        <v>0.3213</v>
       </c>
       <c r="J119" t="n">
-        <v>8.205299999999999</v>
+        <v>8.6751</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2435</v>
+        <v>0.2618</v>
       </c>
       <c r="J120" t="n">
-        <v>6.5745</v>
+        <v>7.0686</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.03</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0402</v>
+        <v>0.0554</v>
       </c>
       <c r="J121" t="n">
-        <v>1.0854</v>
+        <v>1.4958</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.74</v>
       </c>
       <c r="I122" t="n">
-        <v>1.4506</v>
+        <v>1.4309</v>
       </c>
       <c r="J122" t="n">
-        <v>43.518</v>
+        <v>42.927</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3363</v>
+        <v>0.3401</v>
       </c>
       <c r="J123" t="n">
-        <v>10.089</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3085</v>
+        <v>0.3144</v>
       </c>
       <c r="J124" t="n">
-        <v>9.255000000000001</v>
+        <v>9.432</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1257</v>
+        <v>0.1423</v>
       </c>
       <c r="J125" t="n">
-        <v>3.771</v>
+        <v>4.269</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.454</v>
+        <v>-0.4277</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.62</v>
+        <v>-12.831</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2068</v>
+        <v>0.2138</v>
       </c>
       <c r="J127" t="n">
-        <v>6.204</v>
+        <v>6.414</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.04</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1176</v>
+        <v>0.1257</v>
       </c>
       <c r="J128" t="n">
-        <v>3.528</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0674</v>
+        <v>0.0743</v>
       </c>
       <c r="J129" t="n">
-        <v>2.022</v>
+        <v>2.229</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.93</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0992</v>
+        <v>-0.1109</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.976</v>
+        <v>-3.327</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.89</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1444</v>
+        <v>-0.1575</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.332</v>
+        <v>-4.725</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.83</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5641</v>
+        <v>1.5494</v>
       </c>
       <c r="J132" t="n">
-        <v>43.7948</v>
+        <v>43.3832</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5414</v>
+        <v>0.5271</v>
       </c>
       <c r="J133" t="n">
-        <v>15.1592</v>
+        <v>14.7588</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.04</v>
+        <v>-0.0275</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.12</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3358</v>
+        <v>-0.3195</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.4024</v>
+        <v>-8.946</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4236</v>
+        <v>-0.4004</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.8608</v>
+        <v>-11.2112</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5216</v>
+        <v>0.4983</v>
       </c>
       <c r="J137" t="n">
-        <v>14.6048</v>
+        <v>13.9524</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2089</v>
+        <v>0.2045</v>
       </c>
       <c r="J138" t="n">
-        <v>5.8492</v>
+        <v>5.726</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1714</v>
+        <v>-0.1888</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.7992</v>
+        <v>-5.2864</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.58</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4299</v>
+        <v>-0.4408</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.0372</v>
+        <v>-12.3424</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4668</v>
+        <v>-0.4758</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.0704</v>
+        <v>-13.3224</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5372</v>
+        <v>0.5294</v>
       </c>
       <c r="J142" t="n">
-        <v>15.5788</v>
+        <v>15.3526</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.17</v>
       </c>
       <c r="I143" t="n">
-        <v>0.361</v>
+        <v>0.3658</v>
       </c>
       <c r="J143" t="n">
-        <v>10.469</v>
+        <v>10.6082</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3057</v>
+        <v>0.3136</v>
       </c>
       <c r="J144" t="n">
-        <v>8.8653</v>
+        <v>9.0944</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0443</v>
+        <v>-0.0491</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.2847</v>
+        <v>-1.4239</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1764</v>
+        <v>-0.1876</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.1156</v>
+        <v>-5.4404</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0537</v>
+        <v>0.9979</v>
       </c>
       <c r="J147" t="n">
-        <v>30.5573</v>
+        <v>28.9391</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.38</v>
+        <v>0.3762</v>
       </c>
       <c r="J148" t="n">
-        <v>11.02</v>
+        <v>10.9098</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1476</v>
+        <v>0.1575</v>
       </c>
       <c r="J149" t="n">
-        <v>4.2804</v>
+        <v>4.5675</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0188</v>
+        <v>-0.0128</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.5452</v>
+        <v>-0.3712</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5128</v>
+        <v>-0.4859</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.8712</v>
+        <v>-14.0911</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0725</v>
+        <v>-0.0871</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.6675</v>
+        <v>-2.0033</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1619</v>
+        <v>-0.1789</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.7237</v>
+        <v>-4.1147</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1814</v>
+        <v>-0.1989</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.1722</v>
+        <v>-4.5747</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2111</v>
+        <v>-0.2286</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.8553</v>
+        <v>-5.2578</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2111</v>
+        <v>-0.2286</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.8553</v>
+        <v>-5.2578</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.55</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>1.1679</v>
       </c>
       <c r="J157" t="n">
-        <v>27.6</v>
+        <v>26.8617</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.42</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0317</v>
+        <v>0.9797</v>
       </c>
       <c r="J158" t="n">
-        <v>23.7291</v>
+        <v>22.5331</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.31</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.7694</v>
       </c>
       <c r="J159" t="n">
-        <v>18.653</v>
+        <v>17.6962</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5333</v>
+        <v>0.5216</v>
       </c>
       <c r="J160" t="n">
-        <v>12.2659</v>
+        <v>11.9968</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.63</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.0954</v>
+        <v>-0.9925</v>
       </c>
       <c r="J161" t="n">
-        <v>-25.1942</v>
+        <v>-22.8275</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.07</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2003</v>
+        <v>0.2037</v>
       </c>
       <c r="J162" t="n">
-        <v>5.6084</v>
+        <v>5.7036</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.06</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1779</v>
+        <v>0.1818</v>
       </c>
       <c r="J163" t="n">
-        <v>4.9812</v>
+        <v>5.0904</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.094</v>
+        <v>-0.1069</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.632</v>
+        <v>-2.9932</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1595</v>
+        <v>-0.1745</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.466</v>
+        <v>-4.886</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2806</v>
+        <v>-0.2949</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.8568</v>
+        <v>-8.257199999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.46</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1089</v>
+        <v>1.0652</v>
       </c>
       <c r="J167" t="n">
-        <v>31.0492</v>
+        <v>29.8256</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7219</v>
+        <v>0.6857</v>
       </c>
       <c r="J168" t="n">
-        <v>20.2132</v>
+        <v>19.1996</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3727</v>
+        <v>0.3713</v>
       </c>
       <c r="J169" t="n">
-        <v>10.4356</v>
+        <v>10.3964</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3462</v>
+        <v>0.3468</v>
       </c>
       <c r="J170" t="n">
-        <v>9.6936</v>
+        <v>9.7104</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.68</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.956</v>
+        <v>-0.875</v>
       </c>
       <c r="J171" t="n">
-        <v>-26.768</v>
+        <v>-24.5</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.542</v>
+        <v>0.5167</v>
       </c>
       <c r="J172" t="n">
-        <v>11.924</v>
+        <v>11.3674</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.4991</v>
       </c>
       <c r="J173" t="n">
-        <v>11.4994</v>
+        <v>10.9802</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.72</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2979</v>
+        <v>-0.314</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.5538</v>
+        <v>-6.908</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.54</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4666</v>
+        <v>-0.4756</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.2652</v>
+        <v>-10.4632</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.54</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4666</v>
+        <v>-0.4756</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.2652</v>
+        <v>-10.4632</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.73</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3985</v>
+        <v>1.3827</v>
       </c>
       <c r="J177" t="n">
-        <v>30.767</v>
+        <v>30.4194</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9619</v>
+        <v>0.9092</v>
       </c>
       <c r="J178" t="n">
-        <v>21.1618</v>
+        <v>20.0024</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.37</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9223</v>
+        <v>0.8716</v>
       </c>
       <c r="J179" t="n">
-        <v>20.2906</v>
+        <v>19.1752</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.09</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2485</v>
+        <v>0.2661</v>
       </c>
       <c r="J180" t="n">
-        <v>5.467</v>
+        <v>5.8542</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2429</v>
+        <v>-0.2235</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.3438</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.02</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7399</v>
+        <v>1.7401</v>
       </c>
       <c r="J182" t="n">
-        <v>38.2778</v>
+        <v>38.2822</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8589</v>
+        <v>0.8151</v>
       </c>
       <c r="J183" t="n">
-        <v>18.8958</v>
+        <v>17.9322</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.361</v>
+        <v>0.3694</v>
       </c>
       <c r="J184" t="n">
-        <v>7.942</v>
+        <v>8.126799999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.06</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1592</v>
+        <v>0.1823</v>
       </c>
       <c r="J185" t="n">
-        <v>3.5024</v>
+        <v>4.0106</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.97</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2071</v>
+        <v>-0.1891</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.5562</v>
+        <v>-4.1602</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.099</v>
+        <v>-0.1197</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.178</v>
+        <v>-2.6334</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2567</v>
+        <v>-0.2765</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.6474</v>
+        <v>-6.083</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.75</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2567</v>
+        <v>-0.2765</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.6474</v>
+        <v>-6.083</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.321</v>
+        <v>-0.3393</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.062</v>
+        <v>-7.4646</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3679</v>
+        <v>-0.3843</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.0938</v>
+        <v>-8.454599999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.34</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9002</v>
+        <v>0.8438</v>
       </c>
       <c r="J192" t="n">
-        <v>27.006</v>
+        <v>25.314</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7605</v>
+        <v>0.7214</v>
       </c>
       <c r="J193" t="n">
-        <v>22.815</v>
+        <v>21.642</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5288</v>
       </c>
       <c r="J194" t="n">
-        <v>16.317</v>
+        <v>15.864</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2847</v>
+        <v>0.2912</v>
       </c>
       <c r="J195" t="n">
-        <v>8.541</v>
+        <v>8.736000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.87</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4768</v>
+        <v>-0.4495</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.304</v>
+        <v>-13.485</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4359</v>
+        <v>0.4281</v>
       </c>
       <c r="J197" t="n">
-        <v>13.077</v>
+        <v>12.843</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1729</v>
+        <v>0.1782</v>
       </c>
       <c r="J198" t="n">
-        <v>5.187</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0751</v>
+        <v>0.0799</v>
       </c>
       <c r="J199" t="n">
-        <v>2.253</v>
+        <v>2.397</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2534</v>
+        <v>-0.2678</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.602</v>
+        <v>-8.034000000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3118</v>
+        <v>-0.3249</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.353999999999999</v>
+        <v>-9.747</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.84</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1404</v>
+        <v>-0.167</v>
       </c>
       <c r="J202" t="n">
-        <v>-2.808</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.66</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3265</v>
+        <v>-0.3472</v>
       </c>
       <c r="J203" t="n">
-        <v>-6.53</v>
+        <v>-6.944</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.65</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3354</v>
+        <v>-0.3558</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.708</v>
+        <v>-7.116</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.54</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4353</v>
+        <v>-0.451</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.706</v>
+        <v>-9.02</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.52</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.454</v>
+        <v>-0.4686</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.08</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.84</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4933</v>
+        <v>1.4884</v>
       </c>
       <c r="J207" t="n">
-        <v>29.866</v>
+        <v>29.768</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.57</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1805</v>
+        <v>1.1555</v>
       </c>
       <c r="J208" t="n">
-        <v>23.61</v>
+        <v>23.11</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>1.0242</v>
+        <v>0.9797</v>
       </c>
       <c r="J209" t="n">
-        <v>20.484</v>
+        <v>19.594</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.31</v>
       </c>
       <c r="I210" t="n">
-        <v>0.7679</v>
+        <v>0.7398</v>
       </c>
       <c r="J210" t="n">
-        <v>15.358</v>
+        <v>14.796</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.11</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2734</v>
+        <v>0.2962</v>
       </c>
       <c r="J211" t="n">
-        <v>5.468</v>
+        <v>5.924</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.51</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9835</v>
+        <v>0.9291</v>
       </c>
       <c r="J212" t="n">
-        <v>29.505</v>
+        <v>27.873</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1005</v>
+        <v>0.1062</v>
       </c>
       <c r="J213" t="n">
-        <v>3.015</v>
+        <v>3.186</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.99</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0174</v>
+        <v>-0.0229</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.522</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.66</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3691</v>
+        <v>-0.3803</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.073</v>
+        <v>-11.409</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4247</v>
+        <v>-0.4337</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.741</v>
+        <v>-13.011</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.35</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9143</v>
+        <v>0.8578</v>
       </c>
       <c r="J217" t="n">
-        <v>27.429</v>
+        <v>25.734</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.22</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.5905</v>
       </c>
       <c r="J218" t="n">
-        <v>18.342</v>
+        <v>17.715</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.5905</v>
       </c>
       <c r="J219" t="n">
-        <v>18.342</v>
+        <v>17.715</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.14</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4157</v>
+        <v>0.413</v>
       </c>
       <c r="J220" t="n">
-        <v>12.471</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.96</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2114</v>
+        <v>-0.2014</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.342</v>
+        <v>-6.042</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2</v>
       </c>
       <c r="I222" t="n">
-        <v>1.7538</v>
+        <v>1.749</v>
       </c>
       <c r="J222" t="n">
-        <v>43.845</v>
+        <v>43.725</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.536</v>
+        <v>0.5235</v>
       </c>
       <c r="J223" t="n">
-        <v>13.4</v>
+        <v>13.0875</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.17</v>
       </c>
       <c r="I224" t="n">
-        <v>0.487</v>
+        <v>0.4791</v>
       </c>
       <c r="J224" t="n">
-        <v>12.175</v>
+        <v>11.9775</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.84</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.571</v>
+        <v>-0.5321</v>
       </c>
       <c r="J225" t="n">
-        <v>-14.275</v>
+        <v>-13.3025</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.82</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.624</v>
+        <v>-0.5796</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.6</v>
+        <v>-14.49</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5996</v>
+        <v>0.5754</v>
       </c>
       <c r="J227" t="n">
-        <v>14.99</v>
+        <v>14.385</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.02</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0849</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>2.1225</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1781</v>
+        <v>-0.1939</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.4525</v>
+        <v>-4.8475</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2781</v>
+        <v>-0.293</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.9525</v>
+        <v>-7.325</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3357</v>
+        <v>-0.349</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.3925</v>
+        <v>-8.725</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1568</v>
+        <v>1.1178</v>
       </c>
       <c r="J232" t="n">
-        <v>39.3312</v>
+        <v>38.0052</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5959</v>
+        <v>0.5748</v>
       </c>
       <c r="J233" t="n">
-        <v>20.2606</v>
+        <v>19.5432</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2874</v>
+        <v>0.2931</v>
       </c>
       <c r="J234" t="n">
-        <v>9.771599999999999</v>
+        <v>9.965400000000001</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0338</v>
+        <v>-0.0232</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.1492</v>
+        <v>-0.7887999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.91</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3593</v>
+        <v>-0.3427</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.2162</v>
+        <v>-11.6518</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.29</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6219</v>
+        <v>0.5979</v>
       </c>
       <c r="J237" t="n">
-        <v>21.1446</v>
+        <v>20.3286</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.02</v>
       </c>
       <c r="I238" t="n">
-        <v>0.077</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>2.618</v>
+        <v>2.7608</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1816</v>
+        <v>-0.1966</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.1744</v>
+        <v>-6.6844</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2425</v>
+        <v>-0.2573</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.244999999999999</v>
+        <v>-8.748200000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2525</v>
+        <v>-0.267</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.585000000000001</v>
+        <v>-9.077999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.59</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1986</v>
+        <v>1.1761</v>
       </c>
       <c r="J242" t="n">
-        <v>23.972</v>
+        <v>23.522</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.58</v>
       </c>
       <c r="I243" t="n">
-        <v>1.1869</v>
+        <v>1.1636</v>
       </c>
       <c r="J243" t="n">
-        <v>23.738</v>
+        <v>23.272</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I244" t="n">
-        <v>1.1405</v>
+        <v>1.1133</v>
       </c>
       <c r="J244" t="n">
-        <v>22.81</v>
+        <v>22.266</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.48</v>
       </c>
       <c r="I245" t="n">
-        <v>1.0714</v>
+        <v>1.0361</v>
       </c>
       <c r="J245" t="n">
-        <v>21.428</v>
+        <v>20.722</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.29</v>
       </c>
       <c r="I246" t="n">
-        <v>0.7141</v>
+        <v>0.694</v>
       </c>
       <c r="J246" t="n">
-        <v>14.282</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1872</v>
+        <v>-0.2163</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.744</v>
+        <v>-4.326</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.74</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2312</v>
+        <v>-0.2586</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.624</v>
+        <v>-5.172</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.53</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4335</v>
+        <v>-0.4511</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.67</v>
+        <v>-9.022</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.43</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5278</v>
+        <v>-0.5391</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.556</v>
+        <v>-10.782</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.43</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5278</v>
+        <v>-0.5391</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.556</v>
+        <v>-10.782</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.3</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7946</v>
+        <v>0.7537</v>
       </c>
       <c r="J252" t="n">
-        <v>20.6596</v>
+        <v>19.5962</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.3</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7946</v>
+        <v>0.7537</v>
       </c>
       <c r="J253" t="n">
-        <v>20.6596</v>
+        <v>19.5962</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.25</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6784</v>
+        <v>0.651</v>
       </c>
       <c r="J254" t="n">
-        <v>17.6384</v>
+        <v>16.926</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3856</v>
+        <v>0.3864</v>
       </c>
       <c r="J255" t="n">
-        <v>10.0256</v>
+        <v>10.0464</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0476</v>
+        <v>-0.0329</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.2376</v>
+        <v>-0.8554</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.13</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3247</v>
+        <v>0.323</v>
       </c>
       <c r="J257" t="n">
-        <v>8.4422</v>
+        <v>8.398</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.12</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3045</v>
+        <v>0.304</v>
       </c>
       <c r="J258" t="n">
-        <v>7.917</v>
+        <v>7.904</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0829</v>
+        <v>-0.095</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.1554</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.93</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.1071</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.4518</v>
+        <v>-2.7846</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.58</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4411</v>
+        <v>-0.4496</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.4686</v>
+        <v>-11.6896</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4926/event_4926_evp_summary.xlsx
+++ b/database/event/4926/event_4926_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3003</v>
+        <v>6.3619</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3576</v>
+        <v>2.3807</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2438</v>
+        <v>2.2924</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3003</v>
+        <v>6.3619</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6726</v>
+        <v>2.7533</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6277</v>
+        <v>3.6086</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9238</v>
+        <v>3.8946</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1188</v>
+        <v>2.1867</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6277</v>
+        <v>3.6086</v>
       </c>
       <c r="K2" t="n">
         <v>86</v>
@@ -529,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>5.746499999999999</v>
+        <v>5.7953</v>
       </c>
       <c r="N2" t="n">
         <v>246</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8401</v>
+        <v>5.7875</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1854</v>
+        <v>2.1657</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0343</v>
+        <v>2.0307</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8401</v>
+        <v>5.7875</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7317</v>
+        <v>2.7524</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1084</v>
+        <v>3.0351</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1188</v>
+        <v>3.891</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2241</v>
+        <v>2.1847</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1084</v>
+        <v>3.0351</v>
       </c>
       <c r="K3" t="n">
         <v>86</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3325</v>
+        <v>5.219799999999999</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4928</v>
+        <v>5.3608</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0554</v>
+        <v>2.0061</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8762</v>
+        <v>1.8363</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4928</v>
+        <v>5.3608</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8902</v>
+        <v>2.8894</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6026</v>
+        <v>2.4714</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6416</v>
+        <v>4.4056</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5064</v>
+        <v>2.4736</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6026</v>
+        <v>2.4714</v>
       </c>
       <c r="K4" t="n">
         <v>70</v>
@@ -621,7 +621,7 @@
         <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>5.109</v>
+        <v>4.945</v>
       </c>
       <c r="N4" t="n">
         <v>225</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0974</v>
+        <v>4.0882</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5333</v>
+        <v>1.5298</v>
       </c>
       <c r="D5" t="n">
-        <v>1.241</v>
+        <v>1.2566</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0974</v>
+        <v>4.0882</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2318</v>
+        <v>3.1977</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8656</v>
+        <v>0.8905</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7686</v>
+        <v>5.5631</v>
       </c>
       <c r="I5" t="n">
-        <v>3.115</v>
+        <v>3.1235</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8656</v>
+        <v>0.8905</v>
       </c>
       <c r="K5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9806</v>
+        <v>4.014</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0014</v>
+        <v>3.8179</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4974</v>
+        <v>1.4287</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1973</v>
+        <v>1.1334</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0014</v>
+        <v>3.8179</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8573</v>
+        <v>1.7057</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1441</v>
+        <v>2.1122</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8573</v>
+        <v>1.7057</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0029</v>
+        <v>0.9577</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1441</v>
+        <v>2.1122</v>
       </c>
       <c r="K6" t="n">
         <v>86</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>3.147</v>
+        <v>3.0699</v>
       </c>
       <c r="N6" t="n">
         <v>246</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4448</v>
+        <v>3.4494</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2891</v>
+        <v>1.2908</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9439</v>
+        <v>0.9656</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4448</v>
+        <v>3.4494</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9182</v>
+        <v>2.922</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5266</v>
+        <v>0.5274</v>
       </c>
       <c r="H7" t="n">
-        <v>4.734</v>
+        <v>4.5279</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5563</v>
+        <v>2.5423</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5266</v>
+        <v>0.5274</v>
       </c>
       <c r="K7" t="n">
         <v>70</v>
@@ -759,7 +759,7 @@
         <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0829</v>
+        <v>3.0697</v>
       </c>
       <c r="N7" t="n">
         <v>225</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0117</v>
+        <v>2.938</v>
       </c>
       <c r="C8" t="n">
-        <v>1.127</v>
+        <v>1.0994</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7468</v>
+        <v>0.7326</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0117</v>
+        <v>2.938</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2383</v>
+        <v>3.2057</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2266</v>
+        <v>-0.2677</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7901</v>
+        <v>5.593</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1266</v>
+        <v>3.1403</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2266</v>
+        <v>-0.2677</v>
       </c>
       <c r="K8" t="n">
         <v>70</v>
@@ -805,7 +805,7 @@
         <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.8726</v>
       </c>
       <c r="N8" t="n">
         <v>225</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9467</v>
+        <v>2.9092</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1027</v>
+        <v>1.0886</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7195</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9467</v>
+        <v>2.9092</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3945</v>
+        <v>0.3359</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5522</v>
+        <v>2.5733</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3945</v>
+        <v>0.3359</v>
       </c>
       <c r="I9" t="n">
-        <v>0.213</v>
+        <v>0.1886</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5522</v>
+        <v>2.5733</v>
       </c>
       <c r="K9" t="n">
         <v>86</v>
@@ -851,7 +851,7 @@
         <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7652</v>
+        <v>2.7619</v>
       </c>
       <c r="N9" t="n">
         <v>246</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6066</v>
+        <v>2.6171</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9754</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5624</v>
+        <v>0.5864</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6066</v>
+        <v>2.6171</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5118</v>
+        <v>2.5349</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0948</v>
+        <v>0.0822</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3932</v>
+        <v>3.0744</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8323</v>
+        <v>1.7262</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0948</v>
+        <v>0.0822</v>
       </c>
       <c r="K10" t="n">
         <v>161</v>
@@ -897,7 +897,7 @@
         <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9271</v>
+        <v>1.8084</v>
       </c>
       <c r="N10" t="n">
         <v>236</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4775</v>
+        <v>2.1384</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9271</v>
+        <v>0.8002</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5036</v>
+        <v>0.3684</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4775</v>
+        <v>2.1384</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9521</v>
+        <v>1.6947</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5254</v>
+        <v>0.4437</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9521</v>
+        <v>1.6947</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0541</v>
+        <v>0.9515</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5254</v>
+        <v>0.4437</v>
       </c>
       <c r="K11" t="n">
         <v>131</v>
@@ -943,7 +943,7 @@
         <v>70</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5795</v>
+        <v>1.3952</v>
       </c>
       <c r="N11" t="n">
         <v>201</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1189</v>
+        <v>2.0697</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7929</v>
+        <v>0.7745</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3404</v>
+        <v>0.3371</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1189</v>
+        <v>2.0697</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1189</v>
+        <v>2.0697</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1189</v>
+        <v>2.0697</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1189</v>
+        <v>2.0697</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1189</v>
+        <v>2.0697</v>
       </c>
       <c r="N12" t="n">
         <v>131</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0757</v>
+        <v>2.0476</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7662</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3207</v>
+        <v>0.327</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0757</v>
+        <v>2.0476</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0017</v>
+        <v>2.0005</v>
       </c>
       <c r="G13" t="n">
-        <v>0.074</v>
+        <v>0.0471</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0017</v>
+        <v>2.0005</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0809</v>
+        <v>1.1232</v>
       </c>
       <c r="J13" t="n">
-        <v>0.074</v>
+        <v>0.0471</v>
       </c>
       <c r="K13" t="n">
         <v>161</v>
@@ -1035,7 +1035,7 @@
         <v>75</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1549</v>
+        <v>1.1703</v>
       </c>
       <c r="N13" t="n">
         <v>236</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0514</v>
+        <v>1.9816</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7415</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3096</v>
+        <v>0.2969</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0514</v>
+        <v>1.9816</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0514</v>
+        <v>1.9816</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0514</v>
+        <v>1.9816</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0514</v>
+        <v>1.9816</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0514</v>
+        <v>1.9816</v>
       </c>
       <c r="N14" t="n">
         <v>131</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0344</v>
+        <v>1.9193</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7613</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3019</v>
+        <v>0.2685</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0344</v>
+        <v>1.9193</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5371</v>
+        <v>2.0092</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4973</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5371</v>
+        <v>2.0092</v>
       </c>
       <c r="I15" t="n">
-        <v>0.83</v>
+        <v>1.1281</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4973</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>131</v>
@@ -1127,7 +1127,7 @@
         <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3273</v>
+        <v>1.0382</v>
       </c>
       <c r="N15" t="n">
         <v>201</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8651</v>
+        <v>1.8961</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6979</v>
+        <v>0.7095</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2248</v>
+        <v>0.258</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8651</v>
+        <v>1.8961</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9458</v>
+        <v>2.4069</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.5108</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9458</v>
+        <v>2.5939</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0507</v>
+        <v>1.4564</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.5108</v>
       </c>
       <c r="K16" t="n">
         <v>131</v>
@@ -1173,7 +1173,7 @@
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>0.97</v>
+        <v>0.9455999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>201</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8302</v>
+        <v>1.8948</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6849</v>
+        <v>0.709</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2089</v>
+        <v>0.2574</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8302</v>
+        <v>1.8948</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3585</v>
+        <v>1.7926</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5283</v>
+        <v>0.1022</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8873</v>
+        <v>1.7926</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5591</v>
+        <v>1.0065</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5283</v>
+        <v>0.1022</v>
       </c>
       <c r="K17" t="n">
         <v>131</v>
@@ -1219,7 +1219,7 @@
         <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0308</v>
+        <v>1.1087</v>
       </c>
       <c r="N17" t="n">
         <v>201</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7236</v>
+        <v>1.7976</v>
       </c>
       <c r="C18" t="n">
-        <v>0.645</v>
+        <v>0.6727</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1604</v>
+        <v>0.2131</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7236</v>
+        <v>1.7976</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5961</v>
+        <v>1.3595</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1275</v>
+        <v>0.4381</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5961</v>
+        <v>1.3595</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8619</v>
+        <v>0.7633</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1275</v>
+        <v>0.4381</v>
       </c>
       <c r="K18" t="n">
         <v>131</v>
@@ -1265,7 +1265,7 @@
         <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9894000000000001</v>
+        <v>1.2014</v>
       </c>
       <c r="N18" t="n">
         <v>201</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.683</v>
+        <v>1.6704</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6298</v>
+        <v>0.6251</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1419</v>
+        <v>0.1552</v>
       </c>
       <c r="E19" t="n">
-        <v>1.683</v>
+        <v>1.6704</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6935</v>
+        <v>1.7426</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0105</v>
+        <v>-0.0722</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6935</v>
+        <v>1.7426</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9145</v>
+        <v>0.9784</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0105</v>
+        <v>-0.0722</v>
       </c>
       <c r="K19" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="L19" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="M19" t="n">
-        <v>0.904</v>
+        <v>0.9062</v>
       </c>
       <c r="N19" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6777</v>
+        <v>1.5365</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6278</v>
+        <v>0.575</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1395</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6777</v>
+        <v>1.5365</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7269</v>
+        <v>1.5508</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0492</v>
+        <v>-0.0143</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7269</v>
+        <v>1.5508</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9325</v>
+        <v>0.8707</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0492</v>
+        <v>-0.0143</v>
       </c>
       <c r="K20" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="L20" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8833</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3508</v>
+        <v>1.3342</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4993</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3508</v>
+        <v>1.3342</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3508</v>
+        <v>1.3342</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3508</v>
+        <v>1.3342</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3508</v>
+        <v>1.3342</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3508</v>
+        <v>1.3342</v>
       </c>
       <c r="N21" t="n">
         <v>155</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1839</v>
+        <v>0.9804</v>
       </c>
       <c r="C22" t="n">
-        <v>0.443</v>
+        <v>0.3669</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0853</v>
+        <v>-0.1592</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1839</v>
+        <v>0.9804</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1839</v>
+        <v>0.9804</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1839</v>
+        <v>0.9804</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1839</v>
+        <v>0.9804</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1839</v>
+        <v>0.9804</v>
       </c>
       <c r="N22" t="n">
         <v>155</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9845</v>
+        <v>0.9395</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3684</v>
+        <v>0.3516</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.176</v>
+        <v>-0.1778</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9845</v>
+        <v>0.9395</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9845</v>
+        <v>0.9395</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9845</v>
+        <v>0.9395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9845</v>
+        <v>0.9395</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9845</v>
+        <v>0.9395</v>
       </c>
       <c r="N23" t="n">
         <v>155</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7138</v>
+        <v>0.6227</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2671</v>
+        <v>0.233</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2993</v>
+        <v>-0.3221</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7138</v>
+        <v>0.6227</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7138</v>
+        <v>0.6227</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7138</v>
+        <v>0.6227</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7138</v>
+        <v>0.6227</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7138</v>
+        <v>0.6227</v>
       </c>
       <c r="N24" t="n">
         <v>76</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6567</v>
+        <v>0.5591</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2457</v>
+        <v>0.2092</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3253</v>
+        <v>-0.3511</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6567</v>
+        <v>0.5591</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6567</v>
+        <v>0.5591</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6567</v>
+        <v>0.5591</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6567</v>
+        <v>0.5591</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6567</v>
+        <v>0.5591</v>
       </c>
       <c r="N25" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6476</v>
+        <v>0.5048</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2423</v>
+        <v>0.1889</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3294</v>
+        <v>-0.3758</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6476</v>
+        <v>0.5048</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6476</v>
+        <v>0.5048</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6476</v>
+        <v>0.5048</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6476</v>
+        <v>0.5048</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6476</v>
+        <v>0.5048</v>
       </c>
       <c r="N26" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5027</v>
+        <v>0.3632</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1881</v>
+        <v>0.1359</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3954</v>
+        <v>-0.4403</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5027</v>
+        <v>0.3632</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4608</v>
+        <v>1.3741</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9581</v>
+        <v>-1.0109</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4608</v>
+        <v>1.3741</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7715</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9581</v>
+        <v>-1.0109</v>
       </c>
       <c r="K27" t="n">
         <v>70</v>
@@ -1679,7 +1679,7 @@
         <v>155</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1693</v>
+        <v>-0.2393999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2826</v>
+        <v>0.2859</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1058</v>
+        <v>0.107</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4956</v>
+        <v>-0.4755</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2826</v>
+        <v>0.2859</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2826</v>
+        <v>0.2859</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2826</v>
+        <v>0.2859</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2826</v>
+        <v>0.2859</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2826</v>
+        <v>0.2859</v>
       </c>
       <c r="N28" t="n">
         <v>131</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leo_drk</t>
+          <t>Luken</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.185</v>
+        <v>0.1603</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0692</v>
+        <v>0.06</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.54</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.185</v>
+        <v>0.1603</v>
       </c>
       <c r="F29" t="n">
-        <v>0.185</v>
+        <v>0.1603</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.185</v>
+        <v>0.1603</v>
       </c>
       <c r="I29" t="n">
-        <v>0.185</v>
+        <v>0.1603</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.185</v>
+        <v>0.1603</v>
       </c>
       <c r="N29" t="n">
         <v>86</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Luken</t>
+          <t>leo_drk</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1817</v>
+        <v>0.1557</v>
       </c>
       <c r="C30" t="n">
-        <v>0.068</v>
+        <v>0.0583</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5415</v>
+        <v>-0.5349</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1817</v>
+        <v>0.1557</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1817</v>
+        <v>0.1557</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1817</v>
+        <v>0.1557</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1817</v>
+        <v>0.1557</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1817</v>
+        <v>0.1557</v>
       </c>
       <c r="N30" t="n">
         <v>86</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0619</v>
+        <v>-0.0743</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0232</v>
+        <v>-0.0278</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6524</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0619</v>
+        <v>-0.0743</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0619</v>
+        <v>-0.0743</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0619</v>
+        <v>-0.0743</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0619</v>
+        <v>-0.0743</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0619</v>
+        <v>-0.0743</v>
       </c>
       <c r="N31" t="n">
         <v>86</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0375</v>
+        <v>-0.0436</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6698</v>
+        <v>-0.6589</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="N32" t="n">
         <v>86</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1002</v>
+        <v>-0.1186</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0375</v>
+        <v>-0.0444</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6698</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1002</v>
+        <v>-0.1186</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1002</v>
+        <v>-0.1186</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1002</v>
+        <v>-0.1186</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1002</v>
+        <v>-0.1186</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1002</v>
+        <v>-0.1186</v>
       </c>
       <c r="N33" t="n">
         <v>155</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1965</v>
+        <v>-0.1895</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0735</v>
+        <v>-0.0709</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7137</v>
+        <v>-0.6921</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1965</v>
+        <v>-0.1895</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1965</v>
+        <v>-0.1895</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1965</v>
+        <v>-0.1895</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1965</v>
+        <v>-0.1895</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1965</v>
+        <v>-0.1895</v>
       </c>
       <c r="N34" t="n">
         <v>86</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.2393</v>
+        <v>-0.2452</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0895</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7331</v>
+        <v>-0.7175</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2393</v>
+        <v>-0.2452</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2393</v>
+        <v>-0.2452</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2393</v>
+        <v>-0.2452</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2393</v>
+        <v>-0.2452</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.2393</v>
+        <v>-0.2452</v>
       </c>
       <c r="N35" t="n">
         <v>76</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3669</v>
+        <v>-0.39</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1373</v>
+        <v>-0.1459</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7912</v>
+        <v>-0.7835</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3669</v>
+        <v>-0.39</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3669</v>
+        <v>-0.39</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3669</v>
+        <v>-0.39</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3669</v>
+        <v>-0.39</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3669</v>
+        <v>-0.39</v>
       </c>
       <c r="N36" t="n">
         <v>76</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3952</v>
+        <v>-0.4497</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1479</v>
+        <v>-0.1683</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8041</v>
+        <v>-0.8106</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.3952</v>
+        <v>-0.4497</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3952</v>
+        <v>-0.4497</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3952</v>
+        <v>-0.4497</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3952</v>
+        <v>-0.4497</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.3952</v>
+        <v>-0.4497</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.5013</v>
+        <v>-0.6066</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1876</v>
+        <v>-0.227</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8524</v>
+        <v>-0.8821</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5013</v>
+        <v>-0.6066</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4987</v>
+        <v>0.3934</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4987</v>
+        <v>0.3934</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2693</v>
+        <v>0.2209</v>
       </c>
       <c r="J38" t="n">
         <v>-1</v>
@@ -2185,7 +2185,7 @@
         <v>75</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7307</v>
+        <v>-0.7791</v>
       </c>
       <c r="N38" t="n">
         <v>236</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2201</v>
+        <v>-1.1928</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4566</v>
+        <v>-0.4464</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1796</v>
+        <v>-1.1492</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2201</v>
+        <v>-1.1928</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2201</v>
+        <v>-1.1928</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2201</v>
+        <v>-1.1928</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2201</v>
+        <v>-1.1928</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2201</v>
+        <v>-1.1928</v>
       </c>
       <c r="N39" t="n">
         <v>76</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3814</v>
+        <v>-1.2389</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5169</v>
+        <v>-0.4636</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.253</v>
+        <v>-1.1702</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3814</v>
+        <v>-1.2389</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9072</v>
+        <v>-0.7154</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.4742</v>
+        <v>-0.5235</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9072</v>
+        <v>-0.7154</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4899</v>
+        <v>-0.4017</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.4742</v>
+        <v>-0.5235</v>
       </c>
       <c r="K40" t="n">
         <v>161</v>
@@ -2277,7 +2277,7 @@
         <v>75</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9641</v>
+        <v>-0.9252</v>
       </c>
       <c r="N40" t="n">
         <v>236</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8127</v>
+        <v>-1.7633</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6783</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4494</v>
+        <v>-1.4091</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8127</v>
+        <v>-1.7633</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8127</v>
+        <v>-1.7633</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8127</v>
+        <v>-1.7633</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8127</v>
+        <v>-1.7633</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8127</v>
+        <v>-1.7633</v>
       </c>
       <c r="N41" t="n">
         <v>131</v>
@@ -2429,10 +2429,10 @@
         <v>1.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1644</v>
+        <v>0.1478</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5896</v>
+        <v>5.0252</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1141</v>
+        <v>0.0989</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8794</v>
+        <v>3.3626</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1141</v>
+        <v>0.0989</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8794</v>
+        <v>3.3626</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.99</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0262</v>
+        <v>-0.0186</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8908</v>
+        <v>-0.6324</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1368</v>
+        <v>-0.1175</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.6512</v>
+        <v>-3.995</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.64</v>
       </c>
       <c r="I7" t="n">
-        <v>0.794</v>
+        <v>0.7275</v>
       </c>
       <c r="J7" t="n">
-        <v>26.996</v>
+        <v>24.735</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2211</v>
+        <v>0.1748</v>
       </c>
       <c r="J8" t="n">
-        <v>7.5174</v>
+        <v>5.9432</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1207</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1038</v>
+        <v>3.0736</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2078</v>
+        <v>-0.1872</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.0652</v>
+        <v>-6.3648</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3719</v>
+        <v>-0.3598</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.6446</v>
+        <v>-12.2332</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3747</v>
+        <v>1.4142</v>
       </c>
       <c r="J12" t="n">
-        <v>37.1169</v>
+        <v>38.1834</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7528</v>
+        <v>0.723</v>
       </c>
       <c r="J13" t="n">
-        <v>20.3256</v>
+        <v>19.521</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3234</v>
+        <v>0.2869</v>
       </c>
       <c r="J14" t="n">
-        <v>8.7318</v>
+        <v>7.7463</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4159</v>
+        <v>-0.3732</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.2293</v>
+        <v>-10.0764</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.67</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8932</v>
+        <v>-0.8798</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.1164</v>
+        <v>-23.7546</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2653</v>
+        <v>0.2174</v>
       </c>
       <c r="J17" t="n">
-        <v>7.1631</v>
+        <v>5.8698</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0212</v>
+        <v>-0.0157</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5724</v>
+        <v>-0.4239</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0212</v>
+        <v>-0.0157</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5724</v>
+        <v>-0.4239</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0689</v>
+        <v>-0.0563</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8603</v>
+        <v>-1.5201</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3875</v>
+        <v>-0.3755</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.4625</v>
+        <v>-10.1385</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.89</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7296</v>
+        <v>1.7675</v>
       </c>
       <c r="J22" t="n">
-        <v>41.5104</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8572</v>
+        <v>0.8398</v>
       </c>
       <c r="J23" t="n">
-        <v>20.5728</v>
+        <v>20.1552</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6622</v>
+        <v>0.6351</v>
       </c>
       <c r="J24" t="n">
-        <v>15.8928</v>
+        <v>15.2424</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1563</v>
+        <v>0.1303</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7512</v>
+        <v>3.1272</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5681</v>
+        <v>-0.5333</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.6344</v>
+        <v>-12.7992</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5498</v>
+        <v>0.4947</v>
       </c>
       <c r="J27" t="n">
-        <v>13.1952</v>
+        <v>11.8728</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0917</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>2.2008</v>
+        <v>1.5984</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0165</v>
+        <v>-0.0119</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.396</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.89</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1498</v>
+        <v>-0.132</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.5952</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.32</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.6925</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.9552</v>
+        <v>-16.62</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.02</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1034</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>2.2748</v>
+        <v>2.0944</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.92</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0989</v>
+        <v>-0.0847</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.1758</v>
+        <v>-1.8634</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1233</v>
+        <v>-0.1084</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.7126</v>
+        <v>-2.3848</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3957</v>
+        <v>-0.3839</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.705399999999999</v>
+        <v>-8.4458</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.35</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6301</v>
+        <v>-0.6491</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.8622</v>
+        <v>-14.2802</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.54</v>
       </c>
       <c r="I37" t="n">
-        <v>0.591</v>
+        <v>0.5552</v>
       </c>
       <c r="J37" t="n">
-        <v>13.002</v>
+        <v>12.2144</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.45</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5254</v>
+        <v>0.4871</v>
       </c>
       <c r="J38" t="n">
-        <v>11.5588</v>
+        <v>10.7162</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.42</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5031</v>
+        <v>0.4594</v>
       </c>
       <c r="J39" t="n">
-        <v>11.0682</v>
+        <v>10.1068</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4128</v>
+        <v>0.3541</v>
       </c>
       <c r="J40" t="n">
-        <v>9.0816</v>
+        <v>7.7902</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0435</v>
+        <v>0.0278</v>
       </c>
       <c r="J41" t="n">
-        <v>0.957</v>
+        <v>0.6116</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9629</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>21.1838</v>
+        <v>20.9022</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.51</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9495</v>
+        <v>0.9366</v>
       </c>
       <c r="J43" t="n">
-        <v>20.889</v>
+        <v>20.6052</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.38</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7723</v>
+        <v>0.7599</v>
       </c>
       <c r="J44" t="n">
-        <v>16.9906</v>
+        <v>16.7178</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.19</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4903</v>
+        <v>0.4778</v>
       </c>
       <c r="J45" t="n">
-        <v>10.7866</v>
+        <v>10.5116</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.96</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2242</v>
+        <v>-0.1918</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.9324</v>
+        <v>-4.2196</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.87</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1553</v>
+        <v>-0.1397</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.4166</v>
+        <v>-3.0734</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.84</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1881</v>
+        <v>-0.1724</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.1382</v>
+        <v>-3.7928</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.77</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2583</v>
+        <v>-0.2426</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.6826</v>
+        <v>-5.3372</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3216</v>
+        <v>-0.3064</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.0752</v>
+        <v>-6.7408</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4558</v>
+        <v>-0.4494</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.0276</v>
+        <v>-9.886799999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.35</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7651</v>
+        <v>0.749</v>
       </c>
       <c r="J52" t="n">
-        <v>19.8926</v>
+        <v>19.474</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.26</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6268</v>
+        <v>0.6132</v>
       </c>
       <c r="J53" t="n">
-        <v>16.2968</v>
+        <v>15.9432</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6268</v>
+        <v>0.6132</v>
       </c>
       <c r="J54" t="n">
-        <v>16.2968</v>
+        <v>15.9432</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.278</v>
+        <v>-0.2377</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.228</v>
+        <v>-6.1802</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8698</v>
+        <v>-0.8535</v>
       </c>
       <c r="J56" t="n">
-        <v>-22.6148</v>
+        <v>-22.191</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3439</v>
+        <v>0.2907</v>
       </c>
       <c r="J57" t="n">
-        <v>8.9414</v>
+        <v>7.5582</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.16</v>
+        <v>0.1234</v>
       </c>
       <c r="J58" t="n">
-        <v>4.16</v>
+        <v>3.2084</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.13</v>
+        <v>-0.1122</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.38</v>
+        <v>-2.9172</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2159</v>
+        <v>-0.1957</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.6134</v>
+        <v>-5.0882</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3135</v>
+        <v>-0.296</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.151</v>
+        <v>-7.696</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.42</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8312</v>
+        <v>0.8172</v>
       </c>
       <c r="J62" t="n">
-        <v>19.9488</v>
+        <v>19.6128</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7754</v>
+        <v>0.7621</v>
       </c>
       <c r="J63" t="n">
-        <v>18.6096</v>
+        <v>18.2904</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.32</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6902</v>
+        <v>0.6793</v>
       </c>
       <c r="J64" t="n">
-        <v>16.5648</v>
+        <v>16.3032</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.19</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4932</v>
+        <v>0.481</v>
       </c>
       <c r="J65" t="n">
-        <v>11.8368</v>
+        <v>11.544</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3474</v>
+        <v>0.3153</v>
       </c>
       <c r="J66" t="n">
-        <v>8.3376</v>
+        <v>7.5672</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.08</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2793</v>
+        <v>0.2394</v>
       </c>
       <c r="J67" t="n">
-        <v>6.7032</v>
+        <v>5.7456</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.3904</v>
+        <v>-2.0496</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.278</v>
+        <v>-0.2616</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.672</v>
+        <v>-6.2784</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4494</v>
+        <v>-0.4424</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.7856</v>
+        <v>-10.6176</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.52</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4845</v>
+        <v>-0.4813</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.628</v>
+        <v>-11.5512</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4403</v>
+        <v>0.4463</v>
       </c>
       <c r="J72" t="n">
-        <v>12.7687</v>
+        <v>12.9427</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.18</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3135</v>
+        <v>0.3023</v>
       </c>
       <c r="J73" t="n">
-        <v>9.0915</v>
+        <v>8.7667</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1828</v>
+        <v>0.1659</v>
       </c>
       <c r="J74" t="n">
-        <v>5.3012</v>
+        <v>4.8111</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.73</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3195</v>
+        <v>-0.3027</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.265499999999999</v>
+        <v>-8.7783</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.7</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3473</v>
+        <v>-0.3325</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.0717</v>
+        <v>-9.6425</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4229</v>
+        <v>0.3594</v>
       </c>
       <c r="J77" t="n">
-        <v>12.2641</v>
+        <v>10.4226</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3185</v>
+        <v>0.262</v>
       </c>
       <c r="J78" t="n">
-        <v>9.236499999999999</v>
+        <v>7.598</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2564</v>
+        <v>0.2066</v>
       </c>
       <c r="J79" t="n">
-        <v>7.4356</v>
+        <v>5.9914</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.98</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0511</v>
+        <v>-0.039</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.4819</v>
+        <v>-1.131</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1448</v>
+        <v>-0.1252</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.1992</v>
+        <v>-3.6308</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.48</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9004</v>
+        <v>0.8887</v>
       </c>
       <c r="J82" t="n">
-        <v>19.8088</v>
+        <v>19.5514</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7935</v>
+        <v>0.783</v>
       </c>
       <c r="J83" t="n">
-        <v>17.457</v>
+        <v>17.226</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.39</v>
       </c>
       <c r="I84" t="n">
-        <v>0.78</v>
+        <v>0.7698</v>
       </c>
       <c r="J84" t="n">
-        <v>17.16</v>
+        <v>16.9356</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7533</v>
+        <v>0.7437</v>
       </c>
       <c r="J85" t="n">
-        <v>16.5726</v>
+        <v>16.3614</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.25</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5789</v>
+        <v>0.5755</v>
       </c>
       <c r="J86" t="n">
-        <v>12.7358</v>
+        <v>12.661</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.97</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0276</v>
+        <v>-0.0172</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.6072</v>
+        <v>-0.3784</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.89</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1334</v>
+        <v>-0.1182</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.9348</v>
+        <v>-2.6004</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1449</v>
+        <v>-0.1295</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.1878</v>
+        <v>-2.849</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4477</v>
+        <v>-0.4405</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.849399999999999</v>
+        <v>-9.691000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.46</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.535</v>
+        <v>-0.5384</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.77</v>
+        <v>-11.8448</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.95</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6448</v>
+        <v>1.6898</v>
       </c>
       <c r="J92" t="n">
-        <v>41.12</v>
+        <v>42.245</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.27</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6744</v>
+        <v>0.6508</v>
       </c>
       <c r="J93" t="n">
-        <v>16.86</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.26</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6539</v>
+        <v>0.6294</v>
       </c>
       <c r="J94" t="n">
-        <v>16.3475</v>
+        <v>15.735</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.24</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6123</v>
+        <v>0.5861</v>
       </c>
       <c r="J95" t="n">
-        <v>15.3075</v>
+        <v>14.6525</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0575</v>
+        <v>-0.0538</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.4375</v>
+        <v>-1.345</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.29</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6642</v>
+        <v>0.6243</v>
       </c>
       <c r="J97" t="n">
-        <v>16.605</v>
+        <v>15.6075</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1395</v>
+        <v>-0.1241</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.4875</v>
+        <v>-3.1025</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.74</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2895</v>
+        <v>-0.2724</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.2375</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.62</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3989</v>
+        <v>-0.3873</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.9725</v>
+        <v>-9.682499999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.41</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5817</v>
+        <v>-0.5928</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.5425</v>
+        <v>-14.82</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.24</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.6103</v>
       </c>
       <c r="J102" t="n">
-        <v>18.7253</v>
+        <v>17.6987</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.22</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6022</v>
+        <v>0.5652</v>
       </c>
       <c r="J103" t="n">
-        <v>17.4638</v>
+        <v>16.3908</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6022</v>
+        <v>0.5652</v>
       </c>
       <c r="J104" t="n">
-        <v>17.4638</v>
+        <v>16.3908</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0828</v>
+        <v>0.0654</v>
       </c>
       <c r="J105" t="n">
-        <v>2.4012</v>
+        <v>1.8966</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.87</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4421</v>
+        <v>-0.3997</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.8209</v>
+        <v>-11.5913</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5262</v>
       </c>
       <c r="J107" t="n">
-        <v>16.8519</v>
+        <v>15.2598</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0352</v>
+        <v>-0.0274</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.0208</v>
+        <v>-0.7946</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.88</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1609</v>
+        <v>-0.1424</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.6661</v>
+        <v>-4.1296</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2818</v>
+        <v>-0.2631</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.1722</v>
+        <v>-7.6299</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4195</v>
+        <v>-0.4103</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.1655</v>
+        <v>-11.8987</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.16</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3017</v>
+        <v>0.2907</v>
       </c>
       <c r="J112" t="n">
-        <v>8.145899999999999</v>
+        <v>7.8489</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.96</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0551</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.8117</v>
+        <v>-1.4877</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1177</v>
+        <v>-0.1012</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.1779</v>
+        <v>-2.7324</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.86</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1834</v>
+        <v>-0.1638</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.9518</v>
+        <v>-4.4226</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3582</v>
+        <v>-0.3436</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.6714</v>
+        <v>-9.277200000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4872</v>
+        <v>0.4201</v>
       </c>
       <c r="J117" t="n">
-        <v>13.1544</v>
+        <v>11.3427</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.3</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4113</v>
+        <v>0.349</v>
       </c>
       <c r="J118" t="n">
-        <v>11.1051</v>
+        <v>9.423</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3213</v>
+        <v>0.267</v>
       </c>
       <c r="J119" t="n">
-        <v>8.6751</v>
+        <v>7.209</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2618</v>
+        <v>0.214</v>
       </c>
       <c r="J120" t="n">
-        <v>7.0686</v>
+        <v>5.778</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.03</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0554</v>
+        <v>0.0389</v>
       </c>
       <c r="J121" t="n">
-        <v>1.4958</v>
+        <v>1.0503</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.74</v>
       </c>
       <c r="I122" t="n">
-        <v>1.4309</v>
+        <v>1.462</v>
       </c>
       <c r="J122" t="n">
-        <v>42.927</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3401</v>
+        <v>0.3058</v>
       </c>
       <c r="J123" t="n">
-        <v>10.203</v>
+        <v>9.173999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3144</v>
+        <v>0.2808</v>
       </c>
       <c r="J124" t="n">
-        <v>9.432</v>
+        <v>8.423999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1423</v>
+        <v>0.1183</v>
       </c>
       <c r="J125" t="n">
-        <v>4.269</v>
+        <v>3.549</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4277</v>
+        <v>-0.3863</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.831</v>
+        <v>-11.589</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2138</v>
+        <v>0.1711</v>
       </c>
       <c r="J127" t="n">
-        <v>6.414</v>
+        <v>5.133</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.04</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1257</v>
+        <v>0.0949</v>
       </c>
       <c r="J128" t="n">
-        <v>3.771</v>
+        <v>2.847</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0743</v>
+        <v>0.053</v>
       </c>
       <c r="J129" t="n">
-        <v>2.229</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.93</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1109</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.327</v>
+        <v>-2.799</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.89</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1575</v>
+        <v>-0.1376</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.725</v>
+        <v>-4.128</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.83</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5494</v>
+        <v>1.5923</v>
       </c>
       <c r="J132" t="n">
-        <v>43.3832</v>
+        <v>44.5844</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5271</v>
+        <v>0.4909</v>
       </c>
       <c r="J133" t="n">
-        <v>14.7588</v>
+        <v>13.7452</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0275</v>
+        <v>-0.022</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.77</v>
+        <v>-0.616</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3195</v>
+        <v>-0.2786</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.946</v>
+        <v>-7.8008</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4004</v>
+        <v>-0.3586</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.2112</v>
+        <v>-10.0408</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4983</v>
+        <v>0.4458</v>
       </c>
       <c r="J137" t="n">
-        <v>13.9524</v>
+        <v>12.4824</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2045</v>
+        <v>0.1645</v>
       </c>
       <c r="J138" t="n">
-        <v>5.726</v>
+        <v>4.606</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1888</v>
+        <v>-0.1707</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.2864</v>
+        <v>-4.7796</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.58</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4408</v>
+        <v>-0.4334</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.3424</v>
+        <v>-12.1352</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4758</v>
+        <v>-0.4724</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.3224</v>
+        <v>-13.2272</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5294</v>
+        <v>0.4699</v>
       </c>
       <c r="J142" t="n">
-        <v>15.3526</v>
+        <v>13.6271</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.17</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3658</v>
+        <v>0.3124</v>
       </c>
       <c r="J143" t="n">
-        <v>10.6082</v>
+        <v>9.0596</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3136</v>
+        <v>0.2638</v>
       </c>
       <c r="J144" t="n">
-        <v>9.0944</v>
+        <v>7.6502</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0491</v>
+        <v>-0.0372</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.4239</v>
+        <v>-1.0788</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1876</v>
+        <v>-0.1671</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.4404</v>
+        <v>-4.8459</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9979</v>
+        <v>0.995</v>
       </c>
       <c r="J147" t="n">
-        <v>28.9391</v>
+        <v>28.855</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3762</v>
+        <v>0.3366</v>
       </c>
       <c r="J148" t="n">
-        <v>10.9098</v>
+        <v>9.7614</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1575</v>
+        <v>0.1308</v>
       </c>
       <c r="J149" t="n">
-        <v>4.5675</v>
+        <v>3.7932</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0128</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.3712</v>
+        <v>-0.2523</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4859</v>
+        <v>-0.4439</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.0911</v>
+        <v>-12.8731</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0871</v>
+        <v>-0.074</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.0033</v>
+        <v>-1.702</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1789</v>
+        <v>-0.1611</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.1147</v>
+        <v>-3.7053</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1989</v>
+        <v>-0.1804</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.5747</v>
+        <v>-4.1492</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2286</v>
+        <v>-0.2097</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.2578</v>
+        <v>-4.8231</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2286</v>
+        <v>-0.2097</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.2578</v>
+        <v>-4.8231</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.55</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1679</v>
+        <v>1.1816</v>
       </c>
       <c r="J157" t="n">
-        <v>26.8617</v>
+        <v>27.1768</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.42</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9797</v>
+        <v>0.9736</v>
       </c>
       <c r="J158" t="n">
-        <v>22.5331</v>
+        <v>22.3928</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.31</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7694</v>
+        <v>0.7439</v>
       </c>
       <c r="J159" t="n">
-        <v>17.6962</v>
+        <v>17.1097</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5216</v>
+        <v>0.4883</v>
       </c>
       <c r="J160" t="n">
-        <v>11.9968</v>
+        <v>11.2309</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.63</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9925</v>
+        <v>-0.9942</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.8275</v>
+        <v>-22.8666</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.07</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2037</v>
+        <v>0.1618</v>
       </c>
       <c r="J162" t="n">
-        <v>5.7036</v>
+        <v>4.5304</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.06</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1818</v>
+        <v>0.1425</v>
       </c>
       <c r="J163" t="n">
-        <v>5.0904</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1069</v>
+        <v>-0.0907</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.9932</v>
+        <v>-2.5396</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1745</v>
+        <v>-0.1548</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.886</v>
+        <v>-4.3344</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2949</v>
+        <v>-0.2766</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.257199999999999</v>
+        <v>-7.7448</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.46</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0652</v>
+        <v>1.0732</v>
       </c>
       <c r="J167" t="n">
-        <v>29.8256</v>
+        <v>30.0496</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6857</v>
+        <v>0.6525</v>
       </c>
       <c r="J168" t="n">
-        <v>19.1996</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3713</v>
+        <v>0.3341</v>
       </c>
       <c r="J169" t="n">
-        <v>10.3964</v>
+        <v>9.354799999999999</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3468</v>
+        <v>0.3102</v>
       </c>
       <c r="J170" t="n">
-        <v>9.7104</v>
+        <v>8.685600000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.68</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.875</v>
+        <v>-0.8601</v>
       </c>
       <c r="J171" t="n">
-        <v>-24.5</v>
+        <v>-24.0828</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5167</v>
+        <v>0.4646</v>
       </c>
       <c r="J172" t="n">
-        <v>11.3674</v>
+        <v>10.2212</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4991</v>
+        <v>0.4468</v>
       </c>
       <c r="J173" t="n">
-        <v>10.9802</v>
+        <v>9.829599999999999</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.72</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.314</v>
+        <v>-0.2969</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.908</v>
+        <v>-6.5318</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.54</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4756</v>
+        <v>-0.4721</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.4632</v>
+        <v>-10.3862</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.54</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4756</v>
+        <v>-0.4721</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.4632</v>
+        <v>-10.3862</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.73</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3827</v>
+        <v>1.4067</v>
       </c>
       <c r="J177" t="n">
-        <v>30.4194</v>
+        <v>30.9474</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9092</v>
+        <v>0.8969</v>
       </c>
       <c r="J178" t="n">
-        <v>20.0024</v>
+        <v>19.7318</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.37</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8716</v>
+        <v>0.8566</v>
       </c>
       <c r="J179" t="n">
-        <v>19.1752</v>
+        <v>18.8452</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.09</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2661</v>
+        <v>0.2351</v>
       </c>
       <c r="J180" t="n">
-        <v>5.8542</v>
+        <v>5.1722</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2235</v>
+        <v>-0.1911</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.917</v>
+        <v>-4.2042</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.02</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7401</v>
+        <v>1.7969</v>
       </c>
       <c r="J182" t="n">
-        <v>38.2822</v>
+        <v>39.5318</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8151</v>
+        <v>0.7964</v>
       </c>
       <c r="J183" t="n">
-        <v>17.9322</v>
+        <v>17.5208</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3694</v>
+        <v>0.3373</v>
       </c>
       <c r="J184" t="n">
-        <v>8.126799999999999</v>
+        <v>7.4206</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.06</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1823</v>
+        <v>0.1544</v>
       </c>
       <c r="J185" t="n">
-        <v>4.0106</v>
+        <v>3.3968</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.97</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1891</v>
+        <v>-0.1594</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.1602</v>
+        <v>-3.5068</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1197</v>
+        <v>-0.1046</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.6334</v>
+        <v>-2.3012</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2765</v>
+        <v>-0.2609</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.083</v>
+        <v>-5.7398</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.75</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2765</v>
+        <v>-0.2609</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.083</v>
+        <v>-5.7398</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3393</v>
+        <v>-0.3247</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.4646</v>
+        <v>-7.1434</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3843</v>
+        <v>-0.3719</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.454599999999999</v>
+        <v>-8.181800000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.34</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8438</v>
+        <v>0.8212</v>
       </c>
       <c r="J192" t="n">
-        <v>25.314</v>
+        <v>24.636</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7214</v>
+        <v>0.6908</v>
       </c>
       <c r="J193" t="n">
-        <v>21.642</v>
+        <v>20.724</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.19</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5288</v>
+        <v>0.492</v>
       </c>
       <c r="J194" t="n">
-        <v>15.864</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2912</v>
+        <v>0.2579</v>
       </c>
       <c r="J195" t="n">
-        <v>8.736000000000001</v>
+        <v>7.737</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.87</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4495</v>
+        <v>-0.4079</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.485</v>
+        <v>-12.237</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4281</v>
+        <v>0.3712</v>
       </c>
       <c r="J197" t="n">
-        <v>12.843</v>
+        <v>11.136</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1782</v>
+        <v>0.1393</v>
       </c>
       <c r="J198" t="n">
-        <v>5.346</v>
+        <v>4.179</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0799</v>
+        <v>0.0567</v>
       </c>
       <c r="J199" t="n">
-        <v>2.397</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2678</v>
+        <v>-0.2484</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.034000000000001</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3249</v>
+        <v>-0.3083</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.747</v>
+        <v>-9.249000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.84</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.167</v>
+        <v>-0.1498</v>
       </c>
       <c r="J202" t="n">
-        <v>-3.34</v>
+        <v>-2.996</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.66</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3472</v>
+        <v>-0.3363</v>
       </c>
       <c r="J203" t="n">
-        <v>-6.944</v>
+        <v>-6.726</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.65</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3558</v>
+        <v>-0.3451</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.116</v>
+        <v>-6.902</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.54</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.451</v>
+        <v>-0.4445</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.02</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.52</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4686</v>
+        <v>-0.4636</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.372</v>
+        <v>-9.272</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.84</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4884</v>
+        <v>1.5191</v>
       </c>
       <c r="J207" t="n">
-        <v>29.768</v>
+        <v>30.382</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.57</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1555</v>
+        <v>1.1723</v>
       </c>
       <c r="J208" t="n">
-        <v>23.11</v>
+        <v>23.446</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9797</v>
+        <v>0.9829</v>
       </c>
       <c r="J209" t="n">
-        <v>19.594</v>
+        <v>19.658</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.31</v>
       </c>
       <c r="I210" t="n">
-        <v>0.7398</v>
+        <v>0.7232</v>
       </c>
       <c r="J210" t="n">
-        <v>14.796</v>
+        <v>14.464</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.11</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2962</v>
+        <v>0.2632</v>
       </c>
       <c r="J211" t="n">
-        <v>5.924</v>
+        <v>5.264</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.51</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9291</v>
+        <v>0.8911</v>
       </c>
       <c r="J212" t="n">
-        <v>27.873</v>
+        <v>26.733</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1062</v>
+        <v>0.0781</v>
       </c>
       <c r="J213" t="n">
-        <v>3.186</v>
+        <v>2.343</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.99</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0229</v>
+        <v>-0.0169</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.66</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3803</v>
+        <v>-0.3678</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.409</v>
+        <v>-11.034</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4337</v>
+        <v>-0.4265</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.011</v>
+        <v>-12.795</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.35</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8578</v>
+        <v>0.8369</v>
       </c>
       <c r="J217" t="n">
-        <v>25.734</v>
+        <v>25.107</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.22</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5905</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J218" t="n">
-        <v>17.715</v>
+        <v>16.677</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5905</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>17.715</v>
+        <v>16.677</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.14</v>
       </c>
       <c r="I220" t="n">
-        <v>0.413</v>
+        <v>0.3776</v>
       </c>
       <c r="J220" t="n">
-        <v>12.39</v>
+        <v>11.328</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.96</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2014</v>
+        <v>-0.1669</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.042</v>
+        <v>-5.007</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2</v>
       </c>
       <c r="I222" t="n">
-        <v>1.749</v>
+        <v>1.813</v>
       </c>
       <c r="J222" t="n">
-        <v>43.725</v>
+        <v>45.325</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5235</v>
+        <v>0.4893</v>
       </c>
       <c r="J223" t="n">
-        <v>13.0875</v>
+        <v>12.2325</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.17</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4791</v>
+        <v>0.4446</v>
       </c>
       <c r="J224" t="n">
-        <v>11.9775</v>
+        <v>11.115</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.84</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5321</v>
+        <v>-0.4939</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.3025</v>
+        <v>-12.3475</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.82</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5796</v>
+        <v>-0.5434</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.49</v>
+        <v>-13.585</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5754</v>
+        <v>0.5194</v>
       </c>
       <c r="J227" t="n">
-        <v>14.385</v>
+        <v>12.985</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.02</v>
       </c>
       <c r="I228" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0624</v>
       </c>
       <c r="J228" t="n">
-        <v>2.175</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1939</v>
+        <v>-0.174</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.8475</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.293</v>
+        <v>-0.2746</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.325</v>
+        <v>-6.865</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.349</v>
+        <v>-0.3338</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.725</v>
+        <v>-8.345000000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.5</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1178</v>
+        <v>1.1304</v>
       </c>
       <c r="J232" t="n">
-        <v>38.0052</v>
+        <v>38.4336</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5748</v>
+        <v>0.5381</v>
       </c>
       <c r="J233" t="n">
-        <v>19.5432</v>
+        <v>18.2954</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2931</v>
+        <v>0.2592</v>
       </c>
       <c r="J234" t="n">
-        <v>9.965400000000001</v>
+        <v>8.812799999999999</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0232</v>
+        <v>-0.0179</v>
       </c>
       <c r="J235" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.6086</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.91</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3427</v>
+        <v>-0.301</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.6518</v>
+        <v>-10.234</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.29</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5979</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J237" t="n">
-        <v>20.3286</v>
+        <v>18.3872</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.02</v>
       </c>
       <c r="I238" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="J238" t="n">
-        <v>2.7608</v>
+        <v>1.9652</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1966</v>
+        <v>-0.1763</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.6844</v>
+        <v>-5.9942</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2573</v>
+        <v>-0.2375</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.748200000000001</v>
+        <v>-8.074999999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.267</v>
+        <v>-0.2476</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.077999999999999</v>
+        <v>-8.4184</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.59</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1761</v>
+        <v>1.1945</v>
       </c>
       <c r="J242" t="n">
-        <v>23.522</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.58</v>
       </c>
       <c r="I243" t="n">
-        <v>1.1636</v>
+        <v>1.1818</v>
       </c>
       <c r="J243" t="n">
-        <v>23.272</v>
+        <v>23.636</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I244" t="n">
-        <v>1.1133</v>
+        <v>1.1311</v>
       </c>
       <c r="J244" t="n">
-        <v>22.266</v>
+        <v>22.622</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.48</v>
       </c>
       <c r="I245" t="n">
-        <v>1.0361</v>
+        <v>1.0485</v>
       </c>
       <c r="J245" t="n">
-        <v>20.722</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.29</v>
       </c>
       <c r="I246" t="n">
-        <v>0.694</v>
+        <v>0.6752</v>
       </c>
       <c r="J246" t="n">
-        <v>13.88</v>
+        <v>13.504</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2163</v>
+        <v>-0.1995</v>
       </c>
       <c r="J247" t="n">
-        <v>-4.326</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.74</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2586</v>
+        <v>-0.2448</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.172</v>
+        <v>-4.896</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.53</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4511</v>
+        <v>-0.4459</v>
       </c>
       <c r="J249" t="n">
-        <v>-9.022</v>
+        <v>-8.917999999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.43</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5391</v>
+        <v>-0.5416</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.782</v>
+        <v>-10.832</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.43</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5391</v>
+        <v>-0.5416</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.782</v>
+        <v>-10.832</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.3</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7537</v>
+        <v>0.7264</v>
       </c>
       <c r="J252" t="n">
-        <v>19.5962</v>
+        <v>18.8864</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.3</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7537</v>
+        <v>0.7264</v>
       </c>
       <c r="J253" t="n">
-        <v>19.5962</v>
+        <v>18.8864</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.25</v>
       </c>
       <c r="I254" t="n">
-        <v>0.651</v>
+        <v>0.6192</v>
       </c>
       <c r="J254" t="n">
-        <v>16.926</v>
+        <v>16.0992</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3864</v>
+        <v>0.352</v>
       </c>
       <c r="J255" t="n">
-        <v>10.0464</v>
+        <v>9.151999999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0329</v>
+        <v>-0.0273</v>
       </c>
       <c r="J256" t="n">
-        <v>-0.8554</v>
+        <v>-0.7098</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.13</v>
       </c>
       <c r="I257" t="n">
-        <v>0.323</v>
+        <v>0.271</v>
       </c>
       <c r="J257" t="n">
-        <v>8.398</v>
+        <v>7.046</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.12</v>
       </c>
       <c r="I258" t="n">
-        <v>0.304</v>
+        <v>0.2531</v>
       </c>
       <c r="J258" t="n">
-        <v>7.904</v>
+        <v>6.5806</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.095</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.47</v>
+        <v>-2.0722</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.93</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1071</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.7846</v>
+        <v>-2.3608</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.58</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4496</v>
+        <v>-0.4441</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.6896</v>
+        <v>-11.5466</v>
       </c>
     </row>
   </sheetData>
